--- a/144F20/Topic 3/ConstantGrowthRate.xlsx
+++ b/144F20/Topic 3/ConstantGrowthRate.xlsx
@@ -1,31 +1,32 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gcumail-my.sharepoint.com/personal/richard_ketchersid_gcu_edu/Documents/Course Materials/git/Teaching/144F20/Topic 3/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="10_ncr:80_{FE07CE70-4AD8-4729-8CEC-9EA745513535}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{85967B8F-FE5C-49AE-977A-84CE943D66EB}"/>
+  <xr:revisionPtr revIDLastSave="13" documentId="10_ncr:80_{FE07CE70-4AD8-4729-8CEC-9EA745513535}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8E9B77EE-BBF3-4132-B1D9-EFD68F460FAD}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="12852" windowWidth="23256" windowHeight="12456" xr2:uid="{0E835B87-0F00-4DF3-8488-BA3E1D614520}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{0E835B87-0F00-4DF3-8488-BA3E1D614520}"/>
   </bookViews>
   <sheets>
     <sheet name="Constant Change" sheetId="1" r:id="rId1"/>
-    <sheet name="Constant Percent Change" sheetId="2" r:id="rId2"/>
-    <sheet name="Puzzle 1" sheetId="3" r:id="rId3"/>
-    <sheet name="Puzzle 2" sheetId="4" r:id="rId4"/>
-    <sheet name="Sheet2" sheetId="5" state="hidden" r:id="rId5"/>
-    <sheet name="Sheet1" sheetId="6" state="hidden" r:id="rId6"/>
+    <sheet name="Users" sheetId="7" state="hidden" r:id="rId2"/>
+    <sheet name="Constant Percent Change" sheetId="2" r:id="rId3"/>
+    <sheet name="Puzzle 1" sheetId="3" r:id="rId4"/>
+    <sheet name="Puzzle 2" sheetId="4" r:id="rId5"/>
+    <sheet name="Sheet2" sheetId="5" state="hidden" r:id="rId6"/>
+    <sheet name="Sheet1" sheetId="6" state="hidden" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlchart.v1.0" hidden="1">Sheet2!$D$12:$D$33</definedName>
-    <definedName name="Z_86163F03_5311_4FD3_9F34_A891F9AC9F16_.wvu.Rows" localSheetId="2" hidden="1">'Puzzle 1'!$35:$35</definedName>
-    <definedName name="Z_86163F03_5311_4FD3_9F34_A891F9AC9F16_.wvu.Rows" localSheetId="3" hidden="1">'Puzzle 2'!$38:$39</definedName>
+    <definedName name="Z_86163F03_5311_4FD3_9F34_A891F9AC9F16_.wvu.Rows" localSheetId="3" hidden="1">'Puzzle 1'!$35:$35</definedName>
+    <definedName name="Z_86163F03_5311_4FD3_9F34_A891F9AC9F16_.wvu.Rows" localSheetId="4" hidden="1">'Puzzle 2'!$38:$39</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterate="1"/>
   <customWorkbookViews>
     <customWorkbookView name="Richard Ketchersid - Personal View" guid="{86163F03-5311-4FD3-9F34-A891F9AC9F16}" mergeInterval="0" personalView="1" xWindow="184" yWindow="91" windowWidth="1650" windowHeight="938" activeSheetId="1"/>
   </customWorkbookViews>
@@ -46,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="89">
   <si>
     <t>Period</t>
   </si>
@@ -269,9 +270,6 @@
   </si>
   <si>
     <t>Period (half year)</t>
-  </si>
-  <si>
-    <t>aword</t>
   </si>
   <si>
     <t>Enter your name in D1 on the first tab.</t>
@@ -433,6 +431,15 @@
   </si>
   <si>
     <t>Name (at least 5 letters) ⇒</t>
+  </si>
+  <si>
+    <t>Names</t>
+  </si>
+  <si>
+    <t>Reset</t>
+  </si>
+  <si>
+    <t>Your Name</t>
   </si>
 </sst>
 </file>
@@ -1081,7 +1088,6 @@
   </cellStyleXfs>
   <cellXfs count="123">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1254,7 +1260,6 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1265,27 +1270,54 @@
     <xf numFmtId="0" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1295,9 +1327,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1319,7 +1348,7 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1334,67 +1363,46 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1426,7 +1434,7 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1451,6 +1459,10 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2431,8 +2443,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="3987458" y="3262825"/>
-              <a:ext cx="4572000" cy="2871275"/>
+              <a:off x="3993173" y="3259015"/>
+              <a:ext cx="4572000" cy="2875085"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -2762,535 +2774,524 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6510FEE2-CD01-4CA1-A488-F59DAFBFCB6B}">
-  <dimension ref="A1:P20"/>
+  <dimension ref="A1:O20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="4" max="4" width="9.140625" customWidth="1"/>
+    <col min="4" max="4" width="17.42578125" customWidth="1"/>
     <col min="5" max="5" width="15" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="11.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="21.75" thickBot="1">
-      <c r="A1" s="62" t="s">
-        <v>86</v>
-      </c>
-      <c r="B1" s="63"/>
-      <c r="C1" s="63"/>
-      <c r="D1" s="61" t="s">
-        <v>74</v>
-      </c>
-      <c r="E1" s="73" t="s">
+    <row r="1" spans="1:15" ht="21.75" thickBot="1">
+      <c r="A1" s="74" t="s">
+        <v>85</v>
+      </c>
+      <c r="B1" s="75"/>
+      <c r="C1" s="75"/>
+      <c r="D1" s="59" t="s">
+        <v>88</v>
+      </c>
+      <c r="E1" s="79" t="s">
         <v>44</v>
       </c>
-      <c r="F1" s="74"/>
-      <c r="G1" s="74"/>
-      <c r="H1" s="74"/>
-      <c r="I1" s="74"/>
-      <c r="J1" s="74"/>
-      <c r="K1" s="75"/>
-    </row>
-    <row r="2" spans="1:16">
-      <c r="E2" s="76" t="s">
+      <c r="F1" s="80"/>
+      <c r="G1" s="80"/>
+      <c r="H1" s="80"/>
+      <c r="I1" s="80"/>
+      <c r="J1" s="80"/>
+      <c r="K1" s="81"/>
+    </row>
+    <row r="2" spans="1:15">
+      <c r="E2" s="82" t="s">
         <v>45</v>
       </c>
-      <c r="F2" s="77"/>
-      <c r="G2" s="77"/>
-      <c r="H2" s="77"/>
-      <c r="I2" s="77"/>
-      <c r="J2" s="77"/>
-      <c r="K2" s="78"/>
-    </row>
-    <row r="3" spans="1:16">
-      <c r="E3" s="79"/>
-      <c r="F3" s="80"/>
-      <c r="G3" s="80"/>
-      <c r="H3" s="80"/>
-      <c r="I3" s="80"/>
-      <c r="J3" s="80"/>
-      <c r="K3" s="81"/>
-    </row>
-    <row r="4" spans="1:16" ht="20.25" customHeight="1" thickBot="1">
-      <c r="E4" s="82"/>
-      <c r="F4" s="83"/>
-      <c r="G4" s="83"/>
-      <c r="H4" s="83"/>
-      <c r="I4" s="83"/>
-      <c r="J4" s="83"/>
-      <c r="K4" s="84"/>
-      <c r="M4" s="91" t="s">
-        <v>76</v>
-      </c>
-      <c r="N4" s="91"/>
-      <c r="O4" s="91"/>
-      <c r="P4" s="1"/>
-    </row>
-    <row r="5" spans="1:16">
-      <c r="E5" s="76" t="s">
-        <v>84</v>
-      </c>
-      <c r="F5" s="77"/>
-      <c r="G5" s="77"/>
-      <c r="H5" s="77"/>
-      <c r="I5" s="77"/>
-      <c r="J5" s="77"/>
-      <c r="K5" s="78"/>
-      <c r="M5" s="91"/>
-      <c r="N5" s="91"/>
-      <c r="O5" s="91"/>
-      <c r="P5" s="1"/>
-    </row>
-    <row r="6" spans="1:16" ht="21.75" customHeight="1" thickBot="1">
-      <c r="E6" s="82"/>
-      <c r="F6" s="83"/>
-      <c r="G6" s="83"/>
-      <c r="H6" s="83"/>
-      <c r="I6" s="83"/>
-      <c r="J6" s="83"/>
-      <c r="K6" s="84"/>
-    </row>
-    <row r="7" spans="1:16" ht="15.75" thickBot="1">
-      <c r="A7" s="33" t="s">
+      <c r="F2" s="83"/>
+      <c r="G2" s="83"/>
+      <c r="H2" s="83"/>
+      <c r="I2" s="83"/>
+      <c r="J2" s="83"/>
+      <c r="K2" s="84"/>
+    </row>
+    <row r="3" spans="1:15">
+      <c r="E3" s="85"/>
+      <c r="F3" s="86"/>
+      <c r="G3" s="86"/>
+      <c r="H3" s="86"/>
+      <c r="I3" s="86"/>
+      <c r="J3" s="86"/>
+      <c r="K3" s="87"/>
+    </row>
+    <row r="4" spans="1:15" ht="20.25" customHeight="1" thickBot="1">
+      <c r="E4" s="88"/>
+      <c r="F4" s="89"/>
+      <c r="G4" s="89"/>
+      <c r="H4" s="89"/>
+      <c r="I4" s="89"/>
+      <c r="J4" s="89"/>
+      <c r="K4" s="90"/>
+      <c r="M4" s="61" t="s">
+        <v>75</v>
+      </c>
+      <c r="N4" s="61"/>
+      <c r="O4" s="61"/>
+    </row>
+    <row r="5" spans="1:15">
+      <c r="E5" s="82" t="s">
+        <v>83</v>
+      </c>
+      <c r="F5" s="83"/>
+      <c r="G5" s="83"/>
+      <c r="H5" s="83"/>
+      <c r="I5" s="83"/>
+      <c r="J5" s="83"/>
+      <c r="K5" s="84"/>
+      <c r="M5" s="61"/>
+      <c r="N5" s="61"/>
+      <c r="O5" s="61"/>
+    </row>
+    <row r="6" spans="1:15" ht="21.75" customHeight="1" thickBot="1">
+      <c r="E6" s="88"/>
+      <c r="F6" s="89"/>
+      <c r="G6" s="89"/>
+      <c r="H6" s="89"/>
+      <c r="I6" s="89"/>
+      <c r="J6" s="89"/>
+      <c r="K6" s="90"/>
+    </row>
+    <row r="7" spans="1:15" ht="15.75" thickBot="1">
+      <c r="A7" s="32" t="s">
         <v>0</v>
       </c>
-      <c r="B7" s="64" t="s">
+      <c r="B7" s="68" t="s">
         <v>26</v>
       </c>
-      <c r="C7" s="65"/>
-      <c r="D7" s="33" t="s">
+      <c r="C7" s="70"/>
+      <c r="D7" s="32" t="s">
         <v>1</v>
       </c>
-      <c r="E7" s="33" t="s">
+      <c r="E7" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="F7" s="64" t="s">
+      <c r="F7" s="68" t="s">
         <v>38</v>
       </c>
-      <c r="G7" s="72"/>
-      <c r="H7" s="65"/>
-      <c r="I7" s="64" t="s">
+      <c r="G7" s="69"/>
+      <c r="H7" s="70"/>
+      <c r="I7" s="68" t="s">
         <v>43</v>
       </c>
-      <c r="J7" s="72"/>
-      <c r="K7" s="72"/>
-      <c r="L7" s="65"/>
-    </row>
-    <row r="8" spans="1:16">
-      <c r="A8" s="5">
+      <c r="J7" s="69"/>
+      <c r="K7" s="69"/>
+      <c r="L7" s="70"/>
+    </row>
+    <row r="8" spans="1:15">
+      <c r="A8" s="4">
         <v>0</v>
       </c>
-      <c r="B8" s="9" t="s">
+      <c r="B8" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="C8" s="10">
+      <c r="C8" s="9">
         <f ca="1">MOD(Sheet2!B12,1000)+1000</f>
-        <v>1098</v>
-      </c>
-      <c r="D8" s="5"/>
-      <c r="E8" s="5"/>
-      <c r="F8" s="69"/>
-      <c r="G8" s="70"/>
-      <c r="H8" s="71"/>
-      <c r="I8" s="66"/>
-      <c r="J8" s="67"/>
-      <c r="K8" s="67"/>
-      <c r="L8" s="68"/>
-    </row>
-    <row r="9" spans="1:16">
-      <c r="A9" s="5">
+        <v>1331</v>
+      </c>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="76"/>
+      <c r="G8" s="77"/>
+      <c r="H8" s="78"/>
+      <c r="I8" s="62"/>
+      <c r="J8" s="63"/>
+      <c r="K8" s="63"/>
+      <c r="L8" s="64"/>
+    </row>
+    <row r="9" spans="1:15">
+      <c r="A9" s="4">
         <v>1</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="B9" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="C9" s="11">
+      <c r="C9" s="10">
         <f ca="1">C8+ROUND(SIGN(Sheet2!B$14-Sheet2!B$15)*100*Sheet2!D$15,2)</f>
-        <v>1132.82</v>
-      </c>
-      <c r="D9" s="8">
+        <v>1264.55</v>
+      </c>
+      <c r="D9" s="7">
         <f t="shared" ref="D9:D18" ca="1" si="0">C9-C8</f>
-        <v>34.819999999999936</v>
-      </c>
-      <c r="E9" s="6">
+        <v>-66.450000000000045</v>
+      </c>
+      <c r="E9" s="5">
         <f t="shared" ref="E9:E18" ca="1" si="1">C9/C8-1</f>
-        <v>3.1712204007285916E-2</v>
-      </c>
-      <c r="F9" s="66" t="str">
+        <v>-4.9924868519909849E-2</v>
+      </c>
+      <c r="F9" s="62" t="str">
         <f ca="1">B9&amp;" = "&amp;B8&amp;" + "&amp;ROUND(D9,2)</f>
-        <v>Q₁ = Q₀ + 34.82</v>
-      </c>
-      <c r="G9" s="67"/>
-      <c r="H9" s="68"/>
-      <c r="I9" s="66" t="str">
+        <v>Q₁ = Q₀ + -66.45</v>
+      </c>
+      <c r="G9" s="63"/>
+      <c r="H9" s="64"/>
+      <c r="I9" s="62" t="str">
         <f ca="1">B9&amp;" = "&amp;B8&amp;" + "&amp;B8&amp;"∙("&amp;ROUND(E9*100,2)&amp;"%) = "&amp;B8&amp;"∙(1 + "&amp;ROUND(E9*100,2)&amp;"%)"</f>
-        <v>Q₁ = Q₀ + Q₀∙(3.17%) = Q₀∙(1 + 3.17%)</v>
-      </c>
-      <c r="J9" s="67"/>
-      <c r="K9" s="67"/>
-      <c r="L9" s="68"/>
-      <c r="M9" s="4"/>
-    </row>
-    <row r="10" spans="1:16">
-      <c r="A10" s="5">
+        <v>Q₁ = Q₀ + Q₀∙(-4.99%) = Q₀∙(1 + -4.99%)</v>
+      </c>
+      <c r="J9" s="63"/>
+      <c r="K9" s="63"/>
+      <c r="L9" s="64"/>
+      <c r="M9" s="3"/>
+    </row>
+    <row r="10" spans="1:15">
+      <c r="A10" s="4">
         <v>2</v>
       </c>
-      <c r="B10" s="9" t="s">
+      <c r="B10" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="C10" s="11">
+      <c r="C10" s="10">
         <f ca="1">C9+ROUND(SIGN(Sheet2!B$14-Sheet2!B$15)*100*Sheet2!D$15,2)</f>
-        <v>1167.6399999999999</v>
-      </c>
-      <c r="D10" s="8">
+        <v>1198.0999999999999</v>
+      </c>
+      <c r="D10" s="7">
         <f t="shared" ca="1" si="0"/>
-        <v>34.819999999999936</v>
-      </c>
-      <c r="E10" s="6">
+        <v>-66.450000000000045</v>
+      </c>
+      <c r="E10" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>3.0737451669285543E-2</v>
-      </c>
-      <c r="F10" s="66" t="str">
+        <v>-5.2548337353208741E-2</v>
+      </c>
+      <c r="F10" s="62" t="str">
         <f ca="1">B10&amp;" = "&amp;B9&amp;" + "&amp;ROUND(D10,2)&amp;" = "&amp;B$8&amp;" + "&amp;A10&amp;"∙("&amp;ROUND(D10,2)&amp;")"</f>
-        <v>Q₂ = Q₁ + 34.82 = Q₀ + 2∙(34.82)</v>
-      </c>
-      <c r="G10" s="67"/>
-      <c r="H10" s="68"/>
-      <c r="I10" s="66" t="str">
+        <v>Q₂ = Q₁ + -66.45 = Q₀ + 2∙(-66.45)</v>
+      </c>
+      <c r="G10" s="63"/>
+      <c r="H10" s="64"/>
+      <c r="I10" s="62" t="str">
         <f ca="1">B10&amp;" = "&amp;B9&amp;" + "&amp;B9&amp;"∙("&amp;ROUND(E10*100,2)&amp;"%) = "&amp;B9&amp;"∙(1 + "&amp;ROUND(E10*100,2)&amp;"%)"</f>
-        <v>Q₂ = Q₁ + Q₁∙(3.07%) = Q₁∙(1 + 3.07%)</v>
-      </c>
-      <c r="J10" s="67"/>
-      <c r="K10" s="67"/>
-      <c r="L10" s="68"/>
-      <c r="M10" s="1"/>
-    </row>
-    <row r="11" spans="1:16">
-      <c r="A11" s="5">
+        <v>Q₂ = Q₁ + Q₁∙(-5.25%) = Q₁∙(1 + -5.25%)</v>
+      </c>
+      <c r="J10" s="63"/>
+      <c r="K10" s="63"/>
+      <c r="L10" s="64"/>
+    </row>
+    <row r="11" spans="1:15">
+      <c r="A11" s="4">
         <v>3</v>
       </c>
-      <c r="B11" s="9" t="s">
+      <c r="B11" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="C11" s="11">
+      <c r="C11" s="10">
         <f ca="1">C10+ROUND(SIGN(Sheet2!B$14-Sheet2!B$15)*100*Sheet2!D$15,2)</f>
-        <v>1202.4599999999998</v>
-      </c>
-      <c r="D11" s="8">
+        <v>1131.6499999999999</v>
+      </c>
+      <c r="D11" s="7">
         <f t="shared" ca="1" si="0"/>
-        <v>34.819999999999936</v>
-      </c>
-      <c r="E11" s="6">
+        <v>-66.450000000000045</v>
+      </c>
+      <c r="E11" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>2.9820835188927974E-2</v>
-      </c>
-      <c r="F11" s="66" t="str">
+        <v>-5.5462816125532166E-2</v>
+      </c>
+      <c r="F11" s="62" t="str">
         <f ca="1">B11&amp;" = "&amp;B10&amp;" + "&amp;ROUND(D11,2)&amp;" = "&amp;B$8&amp;" + "&amp;A11&amp;"∙("&amp;ROUND(D11,2)&amp;")"</f>
-        <v>Q₃ = Q₂ + 34.82 = Q₀ + 3∙(34.82)</v>
-      </c>
-      <c r="G11" s="67"/>
-      <c r="H11" s="68"/>
-      <c r="I11" s="66" t="str">
+        <v>Q₃ = Q₂ + -66.45 = Q₀ + 3∙(-66.45)</v>
+      </c>
+      <c r="G11" s="63"/>
+      <c r="H11" s="64"/>
+      <c r="I11" s="62" t="str">
         <f t="shared" ref="I11:I17" ca="1" si="2">B11&amp;" = "&amp;B10&amp;" + "&amp;B10&amp;"∙("&amp;ROUND(E11*100,2)&amp;"%) = "&amp;B10&amp;"∙(1 + "&amp;ROUND(E11*100,2)&amp;"%)"</f>
-        <v>Q₃ = Q₂ + Q₂∙(2.98%) = Q₂∙(1 + 2.98%)</v>
-      </c>
-      <c r="J11" s="67"/>
-      <c r="K11" s="67"/>
-      <c r="L11" s="68"/>
-      <c r="M11" s="1"/>
-    </row>
-    <row r="12" spans="1:16">
-      <c r="A12" s="5">
+        <v>Q₃ = Q₂ + Q₂∙(-5.55%) = Q₂∙(1 + -5.55%)</v>
+      </c>
+      <c r="J11" s="63"/>
+      <c r="K11" s="63"/>
+      <c r="L11" s="64"/>
+    </row>
+    <row r="12" spans="1:15">
+      <c r="A12" s="4">
         <v>4</v>
       </c>
-      <c r="B12" s="9" t="s">
+      <c r="B12" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="C12" s="11">
+      <c r="C12" s="10">
         <f ca="1">C11+ROUND(SIGN(Sheet2!B$14-Sheet2!B$15)*100*Sheet2!D$15,2)</f>
-        <v>1237.2799999999997</v>
-      </c>
-      <c r="D12" s="8">
+        <v>1065.1999999999998</v>
+      </c>
+      <c r="D12" s="7">
         <f t="shared" ca="1" si="0"/>
-        <v>34.819999999999936</v>
-      </c>
-      <c r="E12" s="6">
+        <v>-66.450000000000045</v>
+      </c>
+      <c r="E12" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>2.8957304193070854E-2</v>
-      </c>
-      <c r="F12" s="66" t="str">
+        <v>-5.8719568771263275E-2</v>
+      </c>
+      <c r="F12" s="62" t="str">
         <f t="shared" ref="F12:F18" ca="1" si="3">B12&amp;" = "&amp;B11&amp;" + "&amp;ROUND(D12,2)&amp;" = "&amp;B$8&amp;" + "&amp;A12&amp;"∙("&amp;ROUND(D12,2)&amp;")"</f>
-        <v>Q₄ = Q₃ + 34.82 = Q₀ + 4∙(34.82)</v>
-      </c>
-      <c r="G12" s="67"/>
-      <c r="H12" s="68"/>
-      <c r="I12" s="66" t="str">
+        <v>Q₄ = Q₃ + -66.45 = Q₀ + 4∙(-66.45)</v>
+      </c>
+      <c r="G12" s="63"/>
+      <c r="H12" s="64"/>
+      <c r="I12" s="62" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>Q₄ = Q₃ + Q₃∙(2.9%) = Q₃∙(1 + 2.9%)</v>
-      </c>
-      <c r="J12" s="67"/>
-      <c r="K12" s="67"/>
-      <c r="L12" s="68"/>
-      <c r="M12" s="1"/>
-    </row>
-    <row r="13" spans="1:16">
-      <c r="A13" s="5">
+        <v>Q₄ = Q₃ + Q₃∙(-5.87%) = Q₃∙(1 + -5.87%)</v>
+      </c>
+      <c r="J12" s="63"/>
+      <c r="K12" s="63"/>
+      <c r="L12" s="64"/>
+    </row>
+    <row r="13" spans="1:15">
+      <c r="A13" s="4">
         <v>5</v>
       </c>
-      <c r="B13" s="9" t="s">
+      <c r="B13" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="C13" s="11">
+      <c r="C13" s="10">
         <f ca="1">C12+ROUND(SIGN(Sheet2!B$14-Sheet2!B$15)*100*Sheet2!D$15,2)</f>
-        <v>1272.0999999999997</v>
-      </c>
-      <c r="D13" s="8">
+        <v>998.74999999999977</v>
+      </c>
+      <c r="D13" s="7">
         <f t="shared" ca="1" si="0"/>
-        <v>34.819999999999936</v>
-      </c>
-      <c r="E13" s="6">
+        <v>-66.450000000000045</v>
+      </c>
+      <c r="E13" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>2.8142376826587379E-2</v>
-      </c>
-      <c r="F13" s="66" t="str">
+        <v>-6.238265114532493E-2</v>
+      </c>
+      <c r="F13" s="62" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>Q₅ = Q₄ + 34.82 = Q₀ + 5∙(34.82)</v>
-      </c>
-      <c r="G13" s="67"/>
-      <c r="H13" s="68"/>
-      <c r="I13" s="66" t="str">
+        <v>Q₅ = Q₄ + -66.45 = Q₀ + 5∙(-66.45)</v>
+      </c>
+      <c r="G13" s="63"/>
+      <c r="H13" s="64"/>
+      <c r="I13" s="62" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>Q₅ = Q₄ + Q₄∙(2.81%) = Q₄∙(1 + 2.81%)</v>
-      </c>
-      <c r="J13" s="67"/>
-      <c r="K13" s="67"/>
-      <c r="L13" s="68"/>
-      <c r="M13" s="1"/>
-    </row>
-    <row r="14" spans="1:16" ht="15.6" customHeight="1">
-      <c r="A14" s="5">
+        <v>Q₅ = Q₄ + Q₄∙(-6.24%) = Q₄∙(1 + -6.24%)</v>
+      </c>
+      <c r="J13" s="63"/>
+      <c r="K13" s="63"/>
+      <c r="L13" s="64"/>
+    </row>
+    <row r="14" spans="1:15" ht="15.6" customHeight="1">
+      <c r="A14" s="4">
         <v>6</v>
       </c>
-      <c r="B14" s="9" t="s">
+      <c r="B14" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="C14" s="11">
+      <c r="C14" s="10">
         <f ca="1">C13+ROUND(SIGN(Sheet2!B$14-Sheet2!B$15)*100*Sheet2!D$15,2)</f>
-        <v>1306.9199999999996</v>
-      </c>
-      <c r="D14" s="8">
+        <v>932.29999999999973</v>
+      </c>
+      <c r="D14" s="7">
         <f t="shared" ca="1" si="0"/>
-        <v>34.819999999999936</v>
-      </c>
-      <c r="E14" s="6">
+        <v>-66.450000000000045</v>
+      </c>
+      <c r="E14" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>2.7372061944815673E-2</v>
-      </c>
-      <c r="F14" s="66" t="str">
+        <v>-6.6533166458072612E-2</v>
+      </c>
+      <c r="F14" s="62" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>Q₆ = Q₅ + 34.82 = Q₀ + 6∙(34.82)</v>
-      </c>
-      <c r="G14" s="67"/>
-      <c r="H14" s="68"/>
-      <c r="I14" s="66" t="str">
+        <v>Q₆ = Q₅ + -66.45 = Q₀ + 6∙(-66.45)</v>
+      </c>
+      <c r="G14" s="63"/>
+      <c r="H14" s="64"/>
+      <c r="I14" s="62" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>Q₆ = Q₅ + Q₅∙(2.74%) = Q₅∙(1 + 2.74%)</v>
-      </c>
-      <c r="J14" s="67"/>
-      <c r="K14" s="67"/>
-      <c r="L14" s="68"/>
-      <c r="M14" s="1"/>
-    </row>
-    <row r="15" spans="1:16" ht="15.6" customHeight="1">
-      <c r="A15" s="5">
+        <v>Q₆ = Q₅ + Q₅∙(-6.65%) = Q₅∙(1 + -6.65%)</v>
+      </c>
+      <c r="J14" s="63"/>
+      <c r="K14" s="63"/>
+      <c r="L14" s="64"/>
+    </row>
+    <row r="15" spans="1:15" ht="15.6" customHeight="1">
+      <c r="A15" s="4">
         <v>7</v>
       </c>
-      <c r="B15" s="9" t="s">
+      <c r="B15" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="C15" s="11">
+      <c r="C15" s="10">
         <f ca="1">C14+ROUND(SIGN(Sheet2!B$14-Sheet2!B$15)*100*Sheet2!D$15,2)</f>
-        <v>1341.7399999999996</v>
-      </c>
-      <c r="D15" s="8">
+        <v>865.84999999999968</v>
+      </c>
+      <c r="D15" s="7">
         <f t="shared" ca="1" si="0"/>
-        <v>34.819999999999936</v>
-      </c>
-      <c r="E15" s="6">
+        <v>-66.450000000000045</v>
+      </c>
+      <c r="E15" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>2.6642793744070081E-2</v>
-      </c>
-      <c r="F15" s="66" t="str">
+        <v>-7.1275340555615241E-2</v>
+      </c>
+      <c r="F15" s="62" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>Q₇ = Q₆ + 34.82 = Q₀ + 7∙(34.82)</v>
-      </c>
-      <c r="G15" s="67"/>
-      <c r="H15" s="68"/>
-      <c r="I15" s="66" t="str">
+        <v>Q₇ = Q₆ + -66.45 = Q₀ + 7∙(-66.45)</v>
+      </c>
+      <c r="G15" s="63"/>
+      <c r="H15" s="64"/>
+      <c r="I15" s="62" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>Q₇ = Q₆ + Q₆∙(2.66%) = Q₆∙(1 + 2.66%)</v>
-      </c>
-      <c r="J15" s="67"/>
-      <c r="K15" s="67"/>
-      <c r="L15" s="68"/>
-      <c r="M15" s="1"/>
-    </row>
-    <row r="16" spans="1:16" ht="15.6" customHeight="1">
-      <c r="A16" s="5">
+        <v>Q₇ = Q₆ + Q₆∙(-7.13%) = Q₆∙(1 + -7.13%)</v>
+      </c>
+      <c r="J15" s="63"/>
+      <c r="K15" s="63"/>
+      <c r="L15" s="64"/>
+    </row>
+    <row r="16" spans="1:15" ht="15.6" customHeight="1">
+      <c r="A16" s="4">
         <v>8</v>
       </c>
-      <c r="B16" s="9" t="s">
+      <c r="B16" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="C16" s="11">
+      <c r="C16" s="10">
         <f ca="1">C15+ROUND(SIGN(Sheet2!B$14-Sheet2!B$15)*100*Sheet2!D$15,2)</f>
-        <v>1376.5599999999995</v>
-      </c>
-      <c r="D16" s="8">
+        <v>799.39999999999964</v>
+      </c>
+      <c r="D16" s="7">
         <f t="shared" ca="1" si="0"/>
-        <v>34.819999999999936</v>
-      </c>
-      <c r="E16" s="6">
+        <v>-66.450000000000045</v>
+      </c>
+      <c r="E16" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>2.5951376570721552E-2</v>
-      </c>
-      <c r="F16" s="66" t="str">
+        <v>-7.6745394698850888E-2</v>
+      </c>
+      <c r="F16" s="62" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>Q₈ = Q₇ + 34.82 = Q₀ + 8∙(34.82)</v>
-      </c>
-      <c r="G16" s="67"/>
-      <c r="H16" s="68"/>
-      <c r="I16" s="66" t="str">
+        <v>Q₈ = Q₇ + -66.45 = Q₀ + 8∙(-66.45)</v>
+      </c>
+      <c r="G16" s="63"/>
+      <c r="H16" s="64"/>
+      <c r="I16" s="62" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>Q₈ = Q₇ + Q₇∙(2.6%) = Q₇∙(1 + 2.6%)</v>
-      </c>
-      <c r="J16" s="67"/>
-      <c r="K16" s="67"/>
-      <c r="L16" s="68"/>
-      <c r="M16" s="1"/>
-    </row>
-    <row r="17" spans="1:13" ht="15.6" customHeight="1">
-      <c r="A17" s="5">
+        <v>Q₈ = Q₇ + Q₇∙(-7.67%) = Q₇∙(1 + -7.67%)</v>
+      </c>
+      <c r="J16" s="63"/>
+      <c r="K16" s="63"/>
+      <c r="L16" s="64"/>
+    </row>
+    <row r="17" spans="1:12" ht="15.6" customHeight="1">
+      <c r="A17" s="4">
         <v>9</v>
       </c>
-      <c r="B17" s="9" t="s">
+      <c r="B17" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="C17" s="11">
+      <c r="C17" s="10">
         <f ca="1">C16+ROUND(SIGN(Sheet2!B$14-Sheet2!B$15)*100*Sheet2!D$15,2)</f>
-        <v>1411.3799999999994</v>
-      </c>
-      <c r="D17" s="8">
+        <v>732.94999999999959</v>
+      </c>
+      <c r="D17" s="7">
         <f t="shared" ca="1" si="0"/>
-        <v>34.819999999999936</v>
-      </c>
-      <c r="E17" s="6">
+        <v>-66.450000000000045</v>
+      </c>
+      <c r="E17" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>2.5294938106584564E-2</v>
-      </c>
-      <c r="F17" s="66" t="str">
+        <v>-8.3124843632724654E-2</v>
+      </c>
+      <c r="F17" s="62" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>Q₉ = Q₈ + 34.82 = Q₀ + 9∙(34.82)</v>
-      </c>
-      <c r="G17" s="67"/>
-      <c r="H17" s="68"/>
-      <c r="I17" s="66" t="str">
+        <v>Q₉ = Q₈ + -66.45 = Q₀ + 9∙(-66.45)</v>
+      </c>
+      <c r="G17" s="63"/>
+      <c r="H17" s="64"/>
+      <c r="I17" s="62" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>Q₉ = Q₈ + Q₈∙(2.53%) = Q₈∙(1 + 2.53%)</v>
-      </c>
-      <c r="J17" s="67"/>
-      <c r="K17" s="67"/>
-      <c r="L17" s="68"/>
-      <c r="M17" s="1"/>
-    </row>
-    <row r="18" spans="1:13" ht="15.6" customHeight="1">
-      <c r="A18" s="5">
+        <v>Q₉ = Q₈ + Q₈∙(-8.31%) = Q₈∙(1 + -8.31%)</v>
+      </c>
+      <c r="J17" s="63"/>
+      <c r="K17" s="63"/>
+      <c r="L17" s="64"/>
+    </row>
+    <row r="18" spans="1:12" ht="15.6" customHeight="1">
+      <c r="A18" s="4">
         <v>10</v>
       </c>
-      <c r="B18" s="9" t="s">
+      <c r="B18" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="C18" s="11">
+      <c r="C18" s="10">
         <f ca="1">C17+ROUND(SIGN(Sheet2!B$14-Sheet2!B$15)*100*Sheet2!D$15,2)</f>
-        <v>1446.1999999999994</v>
-      </c>
-      <c r="D18" s="8">
+        <v>666.49999999999955</v>
+      </c>
+      <c r="D18" s="7">
         <f t="shared" ca="1" si="0"/>
-        <v>34.819999999999936</v>
-      </c>
-      <c r="E18" s="6">
+        <v>-66.450000000000045</v>
+      </c>
+      <c r="E18" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>2.4670889484051051E-2</v>
-      </c>
-      <c r="F18" s="66" t="str">
+        <v>-9.0661027355208534E-2</v>
+      </c>
+      <c r="F18" s="62" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>Q₁₀ = Q₉ + 34.82 = Q₀ + 10∙(34.82)</v>
-      </c>
-      <c r="G18" s="67"/>
-      <c r="H18" s="68"/>
-      <c r="I18" s="66" t="str">
+        <v>Q₁₀ = Q₉ + -66.45 = Q₀ + 10∙(-66.45)</v>
+      </c>
+      <c r="G18" s="63"/>
+      <c r="H18" s="64"/>
+      <c r="I18" s="62" t="str">
         <f ca="1">B18&amp;" = "&amp;B17&amp;" + "&amp;B17&amp;"∙("&amp;ROUND(E18*100,2)&amp;"%) = "&amp;B17&amp;"∙(1 + "&amp;ROUND(E18*100,2)&amp;"%)"</f>
-        <v>Q₁₀ = Q₉ + Q₉∙(2.47%) = Q₉∙(1 + 2.47%)</v>
-      </c>
-      <c r="J18" s="67"/>
-      <c r="K18" s="67"/>
-      <c r="L18" s="68"/>
-      <c r="M18" s="1"/>
-    </row>
-    <row r="19" spans="1:13">
-      <c r="A19" s="5" t="s">
+        <v>Q₁₀ = Q₉ + Q₉∙(-9.07%) = Q₉∙(1 + -9.07%)</v>
+      </c>
+      <c r="J18" s="63"/>
+      <c r="K18" s="63"/>
+      <c r="L18" s="64"/>
+    </row>
+    <row r="19" spans="1:12">
+      <c r="A19" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="B19" s="9" t="s">
+      <c r="B19" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="C19" s="10" t="s">
+      <c r="C19" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="D19" s="5" t="s">
+      <c r="D19" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="E19" s="5" t="s">
+      <c r="E19" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="F19" s="66" t="str">
+      <c r="F19" s="62" t="str">
         <f>A19</f>
         <v>⋮</v>
       </c>
-      <c r="G19" s="67"/>
-      <c r="H19" s="68"/>
-      <c r="I19" s="66" t="s">
+      <c r="G19" s="63"/>
+      <c r="H19" s="64"/>
+      <c r="I19" s="62" t="s">
         <v>42</v>
       </c>
-      <c r="J19" s="67"/>
-      <c r="K19" s="67"/>
-      <c r="L19" s="68"/>
-    </row>
-    <row r="20" spans="1:13" ht="15.75" thickBot="1">
-      <c r="A20" s="7" t="s">
+      <c r="J19" s="63"/>
+      <c r="K19" s="63"/>
+      <c r="L19" s="64"/>
+    </row>
+    <row r="20" spans="1:12" ht="15.75" thickBot="1">
+      <c r="A20" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B20" s="12" t="s">
+      <c r="B20" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="C20" s="13"/>
-      <c r="D20" s="59">
+      <c r="C20" s="12"/>
+      <c r="D20" s="57">
         <f ca="1">D18</f>
-        <v>34.819999999999936</v>
-      </c>
-      <c r="E20" s="7" t="s">
+        <v>-66.450000000000045</v>
+      </c>
+      <c r="E20" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="F20" s="85" t="str">
+      <c r="F20" s="65" t="str">
         <f ca="1">B20&amp;" = "&amp;B$8&amp;" + "&amp;A20&amp;"∙("&amp;ROUND(D20,2)&amp;")"</f>
-        <v>Qₙ = Q₀ + n∙(34.82)</v>
-      </c>
-      <c r="G20" s="86"/>
-      <c r="H20" s="87"/>
-      <c r="I20" s="88" t="s">
+        <v>Qₙ = Q₀ + n∙(-66.45)</v>
+      </c>
+      <c r="G20" s="66"/>
+      <c r="H20" s="67"/>
+      <c r="I20" s="71" t="s">
         <v>41</v>
       </c>
-      <c r="J20" s="89"/>
-      <c r="K20" s="89"/>
-      <c r="L20" s="90"/>
+      <c r="J20" s="72"/>
+      <c r="K20" s="72"/>
+      <c r="L20" s="73"/>
     </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0"/>
@@ -3302,14 +3303,16 @@
     </customSheetView>
   </customSheetViews>
   <mergeCells count="34">
-    <mergeCell ref="M4:O5"/>
-    <mergeCell ref="I16:L16"/>
-    <mergeCell ref="I17:L17"/>
-    <mergeCell ref="I11:L11"/>
-    <mergeCell ref="I12:L12"/>
-    <mergeCell ref="I13:L13"/>
-    <mergeCell ref="I14:L14"/>
-    <mergeCell ref="I15:L15"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="F9:H9"/>
+    <mergeCell ref="F10:H10"/>
+    <mergeCell ref="F11:H11"/>
+    <mergeCell ref="F8:H8"/>
+    <mergeCell ref="F7:H7"/>
+    <mergeCell ref="E1:K1"/>
+    <mergeCell ref="E2:K4"/>
+    <mergeCell ref="E5:K6"/>
     <mergeCell ref="F20:H20"/>
     <mergeCell ref="F19:H19"/>
     <mergeCell ref="I7:L7"/>
@@ -3326,16 +3329,14 @@
     <mergeCell ref="I19:L19"/>
     <mergeCell ref="I20:L20"/>
     <mergeCell ref="I8:L8"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="F9:H9"/>
-    <mergeCell ref="F10:H10"/>
-    <mergeCell ref="F11:H11"/>
-    <mergeCell ref="F8:H8"/>
-    <mergeCell ref="F7:H7"/>
-    <mergeCell ref="E1:K1"/>
-    <mergeCell ref="E2:K4"/>
-    <mergeCell ref="E5:K6"/>
+    <mergeCell ref="M4:O5"/>
+    <mergeCell ref="I16:L16"/>
+    <mergeCell ref="I17:L17"/>
+    <mergeCell ref="I11:L11"/>
+    <mergeCell ref="I12:L12"/>
+    <mergeCell ref="I13:L13"/>
+    <mergeCell ref="I14:L14"/>
+    <mergeCell ref="I15:L15"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="M4:O5" r:id="rId2" display="https://youtu.be/HoCMAoenzDw" xr:uid="{B7474ABE-EF49-4165-8D07-B721CC234856}"/>
@@ -3347,8 +3348,174 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{054CE7CF-62D4-4C8A-9A68-B26F0F856CD5}">
+  <dimension ref="A1:M21"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="9.140625" style="60"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="60" t="s">
+        <v>86</v>
+      </c>
+      <c r="B1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C1" s="122">
+        <v>1</v>
+      </c>
+      <c r="D1" t="str">
+        <f>'Constant Change'!D1</f>
+        <v>Your Name</v>
+      </c>
+      <c r="F1" s="63" t="str">
+        <f ca="1">IF(M1="ACTIVE", "✓ Tracking Active", "⚠️ ERROR: Enable Iterative Calculations (File &gt; Options &gt; Formulas)")</f>
+        <v>✓ Tracking Active</v>
+      </c>
+      <c r="G1" s="63"/>
+      <c r="H1" s="63"/>
+      <c r="I1" s="63"/>
+      <c r="J1" s="63"/>
+      <c r="K1" s="63"/>
+      <c r="L1" s="63"/>
+      <c r="M1" s="60" t="str">
+        <f ca="1">IF(M1="ACTIVE", "ACTIVE", "ACTIVE")</f>
+        <v>ACTIVE</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="60" t="str">
+        <f t="shared" ref="A2:A19" ca="1" si="0">IF(D$1&lt;&gt;A3,A3,A2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="60" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="60" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="60" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="60" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="60" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="60" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" s="60" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
+      <c r="A10" s="60" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="11" spans="1:13">
+      <c r="A11" s="60" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="12" spans="1:13">
+      <c r="A12" s="60" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="13" spans="1:13">
+      <c r="A13" s="60" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="14" spans="1:13">
+      <c r="A14" s="60" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="15" spans="1:13">
+      <c r="A15" s="60" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="16" spans="1:13">
+      <c r="A16" s="60" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" s="60" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" s="60" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" s="60" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>aword</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" s="60" t="str">
+        <f ca="1">IF(D$1&lt;&gt;A21,A21,A20)</f>
+        <v>aword</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" s="60" t="str">
+        <f ca="1">IF(C1="","",IF(D$1&lt;&gt;A21,D$1,A21))</f>
+        <v>Your Name</v>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection algorithmName="SHA-512" hashValue="PyJZG5r3C5RcAxy4mp/uBJ5GdAkweXsWouZHsOd0Ow65isPuVJIDrnpqC/lDfvZsF5r7dRp8rt0+13U1l1N0+w==" saltValue="aPL74e8iU8fisqsjwESHlA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <mergeCells count="1">
+    <mergeCell ref="F1:L1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04505569-1A4C-40AA-9992-64984D6C147A}">
-  <dimension ref="A1:Q20"/>
+  <dimension ref="A1:O20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="4" max="4" width="7" bestFit="1" customWidth="1"/>
@@ -3357,527 +3524,521 @@
     <col min="13" max="13" width="12.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="15.75" thickBot="1">
-      <c r="E1" s="73" t="s">
-        <v>77</v>
-      </c>
-      <c r="F1" s="72"/>
-      <c r="G1" s="72"/>
-      <c r="H1" s="72"/>
-      <c r="I1" s="72"/>
-      <c r="J1" s="72"/>
-      <c r="K1" s="65"/>
-    </row>
-    <row r="2" spans="1:17">
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="96" t="s">
+    <row r="1" spans="1:15" ht="15.75" thickBot="1">
+      <c r="E1" s="79" t="s">
+        <v>76</v>
+      </c>
+      <c r="F1" s="69"/>
+      <c r="G1" s="69"/>
+      <c r="H1" s="69"/>
+      <c r="I1" s="69"/>
+      <c r="J1" s="69"/>
+      <c r="K1" s="70"/>
+    </row>
+    <row r="2" spans="1:15">
+      <c r="E2" s="93" t="s">
         <v>46</v>
       </c>
-      <c r="F2" s="97"/>
-      <c r="G2" s="97"/>
-      <c r="H2" s="97"/>
-      <c r="I2" s="97"/>
-      <c r="J2" s="97"/>
-      <c r="K2" s="98"/>
-    </row>
-    <row r="3" spans="1:17" ht="15" customHeight="1">
-      <c r="E3" s="99"/>
-      <c r="F3" s="100"/>
-      <c r="G3" s="100"/>
-      <c r="H3" s="100"/>
-      <c r="I3" s="100"/>
-      <c r="J3" s="100"/>
-      <c r="K3" s="101"/>
-      <c r="M3" s="91" t="s">
-        <v>76</v>
-      </c>
-      <c r="N3" s="91"/>
-      <c r="O3" s="91"/>
-      <c r="P3" s="1"/>
-      <c r="Q3" s="1"/>
-    </row>
-    <row r="4" spans="1:17" ht="15.75" thickBot="1">
-      <c r="E4" s="102"/>
-      <c r="F4" s="103"/>
-      <c r="G4" s="103"/>
-      <c r="H4" s="103"/>
-      <c r="I4" s="103"/>
-      <c r="J4" s="103"/>
-      <c r="K4" s="104"/>
-      <c r="M4" s="91"/>
-      <c r="N4" s="91"/>
-      <c r="O4" s="91"/>
-      <c r="P4" s="1"/>
-      <c r="Q4" s="1"/>
-    </row>
-    <row r="5" spans="1:17">
-      <c r="E5" s="96" t="s">
-        <v>85</v>
-      </c>
-      <c r="F5" s="97"/>
-      <c r="G5" s="97"/>
-      <c r="H5" s="97"/>
-      <c r="I5" s="97"/>
-      <c r="J5" s="97"/>
-      <c r="K5" s="98"/>
-    </row>
-    <row r="6" spans="1:17" ht="15.75" thickBot="1">
-      <c r="E6" s="102"/>
-      <c r="F6" s="103"/>
-      <c r="G6" s="103"/>
-      <c r="H6" s="103"/>
-      <c r="I6" s="103"/>
-      <c r="J6" s="103"/>
-      <c r="K6" s="104"/>
-    </row>
-    <row r="7" spans="1:17" ht="15.75" thickBot="1">
-      <c r="A7" s="33" t="s">
+      <c r="F2" s="94"/>
+      <c r="G2" s="94"/>
+      <c r="H2" s="94"/>
+      <c r="I2" s="94"/>
+      <c r="J2" s="94"/>
+      <c r="K2" s="95"/>
+    </row>
+    <row r="3" spans="1:15" ht="15" customHeight="1">
+      <c r="E3" s="96"/>
+      <c r="F3" s="97"/>
+      <c r="G3" s="97"/>
+      <c r="H3" s="97"/>
+      <c r="I3" s="97"/>
+      <c r="J3" s="97"/>
+      <c r="K3" s="98"/>
+      <c r="M3" s="61" t="s">
+        <v>75</v>
+      </c>
+      <c r="N3" s="61"/>
+      <c r="O3" s="61"/>
+    </row>
+    <row r="4" spans="1:15" ht="15.75" thickBot="1">
+      <c r="E4" s="99"/>
+      <c r="F4" s="100"/>
+      <c r="G4" s="100"/>
+      <c r="H4" s="100"/>
+      <c r="I4" s="100"/>
+      <c r="J4" s="100"/>
+      <c r="K4" s="101"/>
+      <c r="M4" s="61"/>
+      <c r="N4" s="61"/>
+      <c r="O4" s="61"/>
+    </row>
+    <row r="5" spans="1:15">
+      <c r="E5" s="93" t="s">
+        <v>84</v>
+      </c>
+      <c r="F5" s="94"/>
+      <c r="G5" s="94"/>
+      <c r="H5" s="94"/>
+      <c r="I5" s="94"/>
+      <c r="J5" s="94"/>
+      <c r="K5" s="95"/>
+    </row>
+    <row r="6" spans="1:15" ht="15.75" thickBot="1">
+      <c r="E6" s="99"/>
+      <c r="F6" s="100"/>
+      <c r="G6" s="100"/>
+      <c r="H6" s="100"/>
+      <c r="I6" s="100"/>
+      <c r="J6" s="100"/>
+      <c r="K6" s="101"/>
+    </row>
+    <row r="7" spans="1:15" ht="15.75" thickBot="1">
+      <c r="A7" s="32" t="s">
         <v>0</v>
       </c>
-      <c r="B7" s="64" t="s">
+      <c r="B7" s="68" t="s">
         <v>26</v>
       </c>
-      <c r="C7" s="65"/>
-      <c r="D7" s="33" t="s">
+      <c r="C7" s="70"/>
+      <c r="D7" s="32" t="s">
         <v>1</v>
       </c>
-      <c r="E7" s="33" t="s">
+      <c r="E7" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="F7" s="64" t="s">
+      <c r="F7" s="68" t="s">
         <v>38</v>
       </c>
-      <c r="G7" s="72"/>
-      <c r="H7" s="72"/>
-      <c r="I7" s="64" t="s">
+      <c r="G7" s="69"/>
+      <c r="H7" s="69"/>
+      <c r="I7" s="68" t="s">
         <v>43</v>
       </c>
-      <c r="J7" s="72"/>
-      <c r="K7" s="72"/>
-      <c r="L7" s="72"/>
-      <c r="M7" s="65"/>
-    </row>
-    <row r="8" spans="1:17">
-      <c r="A8" s="5">
+      <c r="J7" s="69"/>
+      <c r="K7" s="69"/>
+      <c r="L7" s="69"/>
+      <c r="M7" s="70"/>
+    </row>
+    <row r="8" spans="1:15">
+      <c r="A8" s="4">
         <v>0</v>
       </c>
-      <c r="B8" s="9" t="s">
+      <c r="B8" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="C8" s="10">
+      <c r="C8" s="9">
         <f ca="1">MOD(Sheet2!B12,1000)+1000</f>
-        <v>1098</v>
-      </c>
-      <c r="D8" s="5"/>
-      <c r="E8" s="5"/>
-      <c r="F8" s="92"/>
-      <c r="G8" s="93"/>
-      <c r="H8" s="105"/>
-      <c r="I8" s="66"/>
-      <c r="J8" s="67"/>
-      <c r="K8" s="67"/>
-      <c r="L8" s="67"/>
-      <c r="M8" s="68"/>
-    </row>
-    <row r="9" spans="1:17">
-      <c r="A9" s="5">
+        <v>1331</v>
+      </c>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="91"/>
+      <c r="G8" s="92"/>
+      <c r="H8" s="102"/>
+      <c r="I8" s="62"/>
+      <c r="J8" s="63"/>
+      <c r="K8" s="63"/>
+      <c r="L8" s="63"/>
+      <c r="M8" s="64"/>
+    </row>
+    <row r="9" spans="1:15">
+      <c r="A9" s="4">
         <v>1</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="B9" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="C9" s="11">
+      <c r="C9" s="10">
         <f ca="1">C8*ROUND(1+SIGN(Sheet2!B$14-Sheet2!B$15)*Sheet2!D$15%,5)</f>
-        <v>1101.8210399999998</v>
-      </c>
-      <c r="D9" s="8">
+        <v>1322.1621600000001</v>
+      </c>
+      <c r="D9" s="7">
         <f t="shared" ref="D9:D18" ca="1" si="0">C9-C8</f>
-        <v>3.8210399999998117</v>
-      </c>
-      <c r="E9" s="6">
+        <v>-8.8378399999999147</v>
+      </c>
+      <c r="E9" s="5">
         <f t="shared" ref="E9:E18" ca="1" si="1">C9/C8-1</f>
-        <v>3.4799999999999276E-3</v>
-      </c>
-      <c r="F9" s="92" t="str">
+        <v>-6.6399999999999793E-3</v>
+      </c>
+      <c r="F9" s="91" t="str">
         <f ca="1">B9&amp;" = "&amp;B8&amp;" + "&amp;ROUND(D9,2)</f>
-        <v>Q₁ = Q₀ + 3.82</v>
-      </c>
-      <c r="G9" s="93"/>
-      <c r="H9" s="93"/>
-      <c r="I9" s="66" t="str">
+        <v>Q₁ = Q₀ + -8.84</v>
+      </c>
+      <c r="G9" s="92"/>
+      <c r="H9" s="92"/>
+      <c r="I9" s="62" t="str">
         <f ca="1">B9&amp;" = "&amp;B8&amp;" + "&amp;B8&amp;"∙("&amp;ROUND(E9*100,2)&amp;"%) = "&amp;B8&amp;"∙(1 + "&amp;ROUND(E9*100,2)&amp;"%)"</f>
-        <v>Q₁ = Q₀ + Q₀∙(0.35%) = Q₀∙(1 + 0.35%)</v>
-      </c>
-      <c r="J9" s="67"/>
-      <c r="K9" s="67"/>
-      <c r="L9" s="67"/>
-      <c r="M9" s="68"/>
-    </row>
-    <row r="10" spans="1:17">
-      <c r="A10" s="5">
+        <v>Q₁ = Q₀ + Q₀∙(-0.66%) = Q₀∙(1 + -0.66%)</v>
+      </c>
+      <c r="J9" s="63"/>
+      <c r="K9" s="63"/>
+      <c r="L9" s="63"/>
+      <c r="M9" s="64"/>
+    </row>
+    <row r="10" spans="1:15">
+      <c r="A10" s="4">
         <v>2</v>
       </c>
-      <c r="B10" s="9" t="s">
+      <c r="B10" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="C10" s="11">
+      <c r="C10" s="10">
         <f ca="1">C9*ROUND(1+SIGN(Sheet2!B$14-Sheet2!B$15)*Sheet2!D$15%,5)</f>
-        <v>1105.6553772191996</v>
-      </c>
-      <c r="D10" s="8">
+        <v>1313.3830032576002</v>
+      </c>
+      <c r="D10" s="7">
         <f t="shared" ca="1" si="0"/>
-        <v>3.8343372191998242</v>
-      </c>
-      <c r="E10" s="6">
+        <v>-8.7791567423998913</v>
+      </c>
+      <c r="E10" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>3.4799999999999276E-3</v>
-      </c>
-      <c r="F10" s="92" t="str">
+        <v>-6.6399999999998682E-3</v>
+      </c>
+      <c r="F10" s="91" t="str">
         <f ca="1">B10&amp;" = "&amp;B9&amp;" + "&amp;ROUND(D10,2)&amp;""</f>
-        <v>Q₂ = Q₁ + 3.83</v>
-      </c>
-      <c r="G10" s="93"/>
-      <c r="H10" s="93"/>
-      <c r="I10" s="66" t="str">
+        <v>Q₂ = Q₁ + -8.78</v>
+      </c>
+      <c r="G10" s="92"/>
+      <c r="H10" s="92"/>
+      <c r="I10" s="62" t="str">
         <f ca="1">B10&amp;" = "&amp;B9&amp;" + "&amp;B9&amp;"∙("&amp;ROUND(E10*100,2)&amp;"%) = "&amp;B9&amp;"∙(1 + "&amp;ROUND(E10*100,2)&amp;"%) = "&amp;B$8&amp;"∙(1 + "&amp;ROUND(E10*100,2)&amp;"%)²"</f>
-        <v>Q₂ = Q₁ + Q₁∙(0.35%) = Q₁∙(1 + 0.35%) = Q₀∙(1 + 0.35%)²</v>
-      </c>
-      <c r="J10" s="67"/>
-      <c r="K10" s="67"/>
-      <c r="L10" s="67"/>
-      <c r="M10" s="68"/>
-    </row>
-    <row r="11" spans="1:17">
-      <c r="A11" s="5">
+        <v>Q₂ = Q₁ + Q₁∙(-0.66%) = Q₁∙(1 + -0.66%) = Q₀∙(1 + -0.66%)²</v>
+      </c>
+      <c r="J10" s="63"/>
+      <c r="K10" s="63"/>
+      <c r="L10" s="63"/>
+      <c r="M10" s="64"/>
+    </row>
+    <row r="11" spans="1:15">
+      <c r="A11" s="4">
         <v>3</v>
       </c>
-      <c r="B11" s="9" t="s">
+      <c r="B11" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="C11" s="11">
+      <c r="C11" s="10">
         <f ca="1">C10*ROUND(1+SIGN(Sheet2!B$14-Sheet2!B$15)*Sheet2!D$15%,5)</f>
-        <v>1109.5030579319223</v>
-      </c>
-      <c r="D11" s="8">
+        <v>1304.6621401159698</v>
+      </c>
+      <c r="D11" s="7">
         <f t="shared" ca="1" si="0"/>
-        <v>3.8476807127226493</v>
-      </c>
-      <c r="E11" s="6">
+        <v>-8.7208631416303888</v>
+      </c>
+      <c r="E11" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>3.4799999999999276E-3</v>
-      </c>
-      <c r="F11" s="92" t="str">
+        <v>-6.6399999999999793E-3</v>
+      </c>
+      <c r="F11" s="91" t="str">
         <f t="shared" ref="F11:F18" ca="1" si="2">B11&amp;" = "&amp;B10&amp;" + "&amp;ROUND(D11,2)&amp;""</f>
-        <v>Q₃ = Q₂ + 3.85</v>
-      </c>
-      <c r="G11" s="93"/>
-      <c r="H11" s="93"/>
-      <c r="I11" s="66" t="str">
+        <v>Q₃ = Q₂ + -8.72</v>
+      </c>
+      <c r="G11" s="92"/>
+      <c r="H11" s="92"/>
+      <c r="I11" s="62" t="str">
         <f ca="1">B11&amp;" = "&amp;B10&amp;" + "&amp;B10&amp;"∙("&amp;ROUND(E11*100,2)&amp;"%) = "&amp;B10&amp;"∙(1 + "&amp;ROUND(E11*100,2)&amp;"%) = "&amp;B$8&amp;"∙(1 + "&amp;ROUND(E11*100,2)&amp;"%)³"</f>
-        <v>Q₃ = Q₂ + Q₂∙(0.35%) = Q₂∙(1 + 0.35%) = Q₀∙(1 + 0.35%)³</v>
-      </c>
-      <c r="J11" s="67"/>
-      <c r="K11" s="67"/>
-      <c r="L11" s="67"/>
-      <c r="M11" s="68"/>
-    </row>
-    <row r="12" spans="1:17">
-      <c r="A12" s="5">
+        <v>Q₃ = Q₂ + Q₂∙(-0.66%) = Q₂∙(1 + -0.66%) = Q₀∙(1 + -0.66%)³</v>
+      </c>
+      <c r="J11" s="63"/>
+      <c r="K11" s="63"/>
+      <c r="L11" s="63"/>
+      <c r="M11" s="64"/>
+    </row>
+    <row r="12" spans="1:15">
+      <c r="A12" s="4">
         <v>4</v>
       </c>
-      <c r="B12" s="9" t="s">
+      <c r="B12" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="C12" s="11">
+      <c r="C12" s="10">
         <f ca="1">C11*ROUND(1+SIGN(Sheet2!B$14-Sheet2!B$15)*Sheet2!D$15%,5)</f>
-        <v>1113.3641285735252</v>
-      </c>
-      <c r="D12" s="8">
+        <v>1295.9991835055998</v>
+      </c>
+      <c r="D12" s="7">
         <f t="shared" ca="1" si="0"/>
-        <v>3.8610706416029643</v>
-      </c>
-      <c r="E12" s="6">
+        <v>-8.6629566103699744</v>
+      </c>
+      <c r="E12" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>3.4799999999999276E-3</v>
-      </c>
-      <c r="F12" s="92" t="str">
+        <v>-6.6399999999999793E-3</v>
+      </c>
+      <c r="F12" s="91" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>Q₄ = Q₃ + 3.86</v>
-      </c>
-      <c r="G12" s="93"/>
-      <c r="H12" s="93"/>
-      <c r="I12" s="66" t="str">
+        <v>Q₄ = Q₃ + -8.66</v>
+      </c>
+      <c r="G12" s="92"/>
+      <c r="H12" s="92"/>
+      <c r="I12" s="62" t="str">
         <f ca="1">B12&amp;" = "&amp;B11&amp;" + "&amp;B11&amp;"∙("&amp;ROUND(E12*100,2)&amp;"%) = "&amp;B11&amp;"∙(1 + "&amp;ROUND(E12*100,2)&amp;"%) = "&amp;B$8&amp;"∙(1 + "&amp;ROUND(E12*100,2)&amp;"%)⁴"</f>
-        <v>Q₄ = Q₃ + Q₃∙(0.35%) = Q₃∙(1 + 0.35%) = Q₀∙(1 + 0.35%)⁴</v>
-      </c>
-      <c r="J12" s="67"/>
-      <c r="K12" s="67"/>
-      <c r="L12" s="67"/>
-      <c r="M12" s="68"/>
-    </row>
-    <row r="13" spans="1:17">
-      <c r="A13" s="5">
+        <v>Q₄ = Q₃ + Q₃∙(-0.66%) = Q₃∙(1 + -0.66%) = Q₀∙(1 + -0.66%)⁴</v>
+      </c>
+      <c r="J12" s="63"/>
+      <c r="K12" s="63"/>
+      <c r="L12" s="63"/>
+      <c r="M12" s="64"/>
+    </row>
+    <row r="13" spans="1:15">
+      <c r="A13" s="4">
         <v>5</v>
       </c>
-      <c r="B13" s="9" t="s">
+      <c r="B13" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="C13" s="11">
+      <c r="C13" s="10">
         <f ca="1">C12*ROUND(1+SIGN(Sheet2!B$14-Sheet2!B$15)*Sheet2!D$15%,5)</f>
-        <v>1117.2386357409609</v>
-      </c>
-      <c r="D13" s="8">
+        <v>1287.3937489271227</v>
+      </c>
+      <c r="D13" s="7">
         <f t="shared" ca="1" si="0"/>
-        <v>3.874507167435695</v>
-      </c>
-      <c r="E13" s="6">
+        <v>-8.6054345784771158</v>
+      </c>
+      <c r="E13" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>3.4799999999999276E-3</v>
-      </c>
-      <c r="F13" s="92" t="str">
+        <v>-6.6399999999999793E-3</v>
+      </c>
+      <c r="F13" s="91" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>Q₅ = Q₄ + 3.87</v>
-      </c>
-      <c r="G13" s="93"/>
-      <c r="H13" s="93"/>
-      <c r="I13" s="66" t="str">
+        <v>Q₅ = Q₄ + -8.61</v>
+      </c>
+      <c r="G13" s="92"/>
+      <c r="H13" s="92"/>
+      <c r="I13" s="62" t="str">
         <f ca="1">B13&amp;" = "&amp;B12&amp;" + "&amp;B12&amp;"∙("&amp;ROUND(E13*100,2)&amp;"%) = "&amp;B12&amp;"∙(1 + "&amp;ROUND(E13*100,2)&amp;"%) = "&amp;B$8&amp;"∙(1 + "&amp;ROUND(E13*100,2)&amp;"%)⁵"</f>
-        <v>Q₅ = Q₄ + Q₄∙(0.35%) = Q₄∙(1 + 0.35%) = Q₀∙(1 + 0.35%)⁵</v>
-      </c>
-      <c r="J13" s="67"/>
-      <c r="K13" s="67"/>
-      <c r="L13" s="67"/>
-      <c r="M13" s="68"/>
-    </row>
-    <row r="14" spans="1:17" ht="15.6" customHeight="1">
-      <c r="A14" s="5">
+        <v>Q₅ = Q₄ + Q₄∙(-0.66%) = Q₄∙(1 + -0.66%) = Q₀∙(1 + -0.66%)⁵</v>
+      </c>
+      <c r="J13" s="63"/>
+      <c r="K13" s="63"/>
+      <c r="L13" s="63"/>
+      <c r="M13" s="64"/>
+    </row>
+    <row r="14" spans="1:15" ht="15.6" customHeight="1">
+      <c r="A14" s="4">
         <v>6</v>
       </c>
-      <c r="B14" s="9" t="s">
+      <c r="B14" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="C14" s="11">
+      <c r="C14" s="10">
         <f ca="1">C13*ROUND(1+SIGN(Sheet2!B$14-Sheet2!B$15)*Sheet2!D$15%,5)</f>
-        <v>1121.1266261933395</v>
-      </c>
-      <c r="D14" s="8">
+        <v>1278.8454544342467</v>
+      </c>
+      <c r="D14" s="7">
         <f t="shared" ca="1" si="0"/>
-        <v>3.8879904523785171</v>
-      </c>
-      <c r="E14" s="6">
+        <v>-8.5482944928760389</v>
+      </c>
+      <c r="E14" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>3.4799999999999276E-3</v>
-      </c>
-      <c r="F14" s="92" t="str">
+        <v>-6.6399999999999793E-3</v>
+      </c>
+      <c r="F14" s="91" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>Q₆ = Q₅ + 3.89</v>
-      </c>
-      <c r="G14" s="93"/>
-      <c r="H14" s="93"/>
-      <c r="I14" s="66" t="str">
+        <v>Q₆ = Q₅ + -8.55</v>
+      </c>
+      <c r="G14" s="92"/>
+      <c r="H14" s="92"/>
+      <c r="I14" s="62" t="str">
         <f ca="1">B14&amp;" = "&amp;B13&amp;" + "&amp;B13&amp;"∙("&amp;ROUND(E14*100,2)&amp;"%) = "&amp;B13&amp;"∙(1 + "&amp;ROUND(E14*100,2)&amp;"%) = "&amp;B$8&amp;"∙(1 + "&amp;ROUND(E14*100,2)&amp;"%)⁶"</f>
-        <v>Q₆ = Q₅ + Q₅∙(0.35%) = Q₅∙(1 + 0.35%) = Q₀∙(1 + 0.35%)⁶</v>
-      </c>
-      <c r="J14" s="67"/>
-      <c r="K14" s="67"/>
-      <c r="L14" s="67"/>
-      <c r="M14" s="68"/>
-    </row>
-    <row r="15" spans="1:17" ht="15.6" customHeight="1">
-      <c r="A15" s="5">
+        <v>Q₆ = Q₅ + Q₅∙(-0.66%) = Q₅∙(1 + -0.66%) = Q₀∙(1 + -0.66%)⁶</v>
+      </c>
+      <c r="J14" s="63"/>
+      <c r="K14" s="63"/>
+      <c r="L14" s="63"/>
+      <c r="M14" s="64"/>
+    </row>
+    <row r="15" spans="1:15" ht="15.6" customHeight="1">
+      <c r="A15" s="4">
         <v>7</v>
       </c>
-      <c r="B15" s="9" t="s">
+      <c r="B15" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="C15" s="11">
+      <c r="C15" s="10">
         <f ca="1">C14*ROUND(1+SIGN(Sheet2!B$14-Sheet2!B$15)*Sheet2!D$15%,5)</f>
-        <v>1125.0281468524922</v>
-      </c>
-      <c r="D15" s="8">
+        <v>1270.3539206168034</v>
+      </c>
+      <c r="D15" s="7">
         <f t="shared" ca="1" si="0"/>
-        <v>3.9015206591527658</v>
-      </c>
-      <c r="E15" s="6">
+        <v>-8.4915338174432691</v>
+      </c>
+      <c r="E15" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>3.4799999999999276E-3</v>
-      </c>
-      <c r="F15" s="92" t="str">
+        <v>-6.6399999999998682E-3</v>
+      </c>
+      <c r="F15" s="91" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>Q₇ = Q₆ + 3.9</v>
-      </c>
-      <c r="G15" s="93"/>
-      <c r="H15" s="93"/>
-      <c r="I15" s="66" t="str">
+        <v>Q₇ = Q₆ + -8.49</v>
+      </c>
+      <c r="G15" s="92"/>
+      <c r="H15" s="92"/>
+      <c r="I15" s="62" t="str">
         <f ca="1">B15&amp;" = "&amp;B14&amp;" + "&amp;B14&amp;"∙("&amp;ROUND(E15*100,2)&amp;"%) = "&amp;B14&amp;"∙(1 + "&amp;ROUND(E15*100,2)&amp;"%) = "&amp;B$8&amp;"∙(1 + "&amp;ROUND(E15*100,2)&amp;"%)⁷"</f>
-        <v>Q₇ = Q₆ + Q₆∙(0.35%) = Q₆∙(1 + 0.35%) = Q₀∙(1 + 0.35%)⁷</v>
-      </c>
-      <c r="J15" s="67"/>
-      <c r="K15" s="67"/>
-      <c r="L15" s="67"/>
-      <c r="M15" s="68"/>
-    </row>
-    <row r="16" spans="1:17" ht="15.6" customHeight="1">
-      <c r="A16" s="5">
+        <v>Q₇ = Q₆ + Q₆∙(-0.66%) = Q₆∙(1 + -0.66%) = Q₀∙(1 + -0.66%)⁷</v>
+      </c>
+      <c r="J15" s="63"/>
+      <c r="K15" s="63"/>
+      <c r="L15" s="63"/>
+      <c r="M15" s="64"/>
+    </row>
+    <row r="16" spans="1:15" ht="15.6" customHeight="1">
+      <c r="A16" s="4">
         <v>8</v>
       </c>
-      <c r="B16" s="9" t="s">
+      <c r="B16" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="C16" s="11">
+      <c r="C16" s="10">
         <f ca="1">C15*ROUND(1+SIGN(Sheet2!B$14-Sheet2!B$15)*Sheet2!D$15%,5)</f>
-        <v>1128.9432448035388</v>
-      </c>
-      <c r="D16" s="8">
+        <v>1261.9187705839079</v>
+      </c>
+      <c r="D16" s="7">
         <f t="shared" ca="1" si="0"/>
-        <v>3.9150979510466186</v>
-      </c>
-      <c r="E16" s="6">
+        <v>-8.4351500328955353</v>
+      </c>
+      <c r="E16" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>3.4799999999999276E-3</v>
-      </c>
-      <c r="F16" s="92" t="str">
+        <v>-6.6399999999999793E-3</v>
+      </c>
+      <c r="F16" s="91" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>Q₈ = Q₇ + 3.92</v>
-      </c>
-      <c r="G16" s="93"/>
-      <c r="H16" s="93"/>
-      <c r="I16" s="66" t="str">
+        <v>Q₈ = Q₇ + -8.44</v>
+      </c>
+      <c r="G16" s="92"/>
+      <c r="H16" s="92"/>
+      <c r="I16" s="62" t="str">
         <f ca="1">B16&amp;" = "&amp;B15&amp;" + "&amp;B15&amp;"∙("&amp;ROUND(E16*100,2)&amp;"%) = "&amp;B15&amp;"∙(1 + "&amp;ROUND(E16*100,2)&amp;"%) = "&amp;B$8&amp;"∙(1 + "&amp;ROUND(E16*100,2)&amp;"%)⁸"</f>
-        <v>Q₈ = Q₇ + Q₇∙(0.35%) = Q₇∙(1 + 0.35%) = Q₀∙(1 + 0.35%)⁸</v>
-      </c>
-      <c r="J16" s="67"/>
-      <c r="K16" s="67"/>
-      <c r="L16" s="67"/>
-      <c r="M16" s="68"/>
+        <v>Q₈ = Q₇ + Q₇∙(-0.66%) = Q₇∙(1 + -0.66%) = Q₀∙(1 + -0.66%)⁸</v>
+      </c>
+      <c r="J16" s="63"/>
+      <c r="K16" s="63"/>
+      <c r="L16" s="63"/>
+      <c r="M16" s="64"/>
     </row>
     <row r="17" spans="1:13" ht="15.6" customHeight="1">
-      <c r="A17" s="5">
+      <c r="A17" s="4">
         <v>9</v>
       </c>
-      <c r="B17" s="9" t="s">
+      <c r="B17" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="C17" s="11">
+      <c r="C17" s="10">
         <f ca="1">C16*ROUND(1+SIGN(Sheet2!B$14-Sheet2!B$15)*Sheet2!D$15%,5)</f>
-        <v>1132.8719672954551</v>
-      </c>
-      <c r="D17" s="8">
+        <v>1253.5396299472307</v>
+      </c>
+      <c r="D17" s="7">
         <f t="shared" ca="1" si="0"/>
-        <v>3.9287224919162327</v>
-      </c>
-      <c r="E17" s="6">
+        <v>-8.3791406366772208</v>
+      </c>
+      <c r="E17" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>3.4799999999999276E-3</v>
-      </c>
-      <c r="F17" s="92" t="str">
+        <v>-6.6400000000000903E-3</v>
+      </c>
+      <c r="F17" s="91" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>Q₉ = Q₈ + 3.93</v>
-      </c>
-      <c r="G17" s="93"/>
-      <c r="H17" s="93"/>
-      <c r="I17" s="66" t="str">
+        <v>Q₉ = Q₈ + -8.38</v>
+      </c>
+      <c r="G17" s="92"/>
+      <c r="H17" s="92"/>
+      <c r="I17" s="62" t="str">
         <f ca="1">B17&amp;" = "&amp;B16&amp;" + "&amp;B16&amp;"∙("&amp;ROUND(E17*100,2)&amp;"%) = "&amp;B16&amp;"∙(1 + "&amp;ROUND(E17*100,2)&amp;"%) = "&amp;B$8&amp;"∙(1 + "&amp;ROUND(E17*100,2)&amp;"%)⁹"</f>
-        <v>Q₉ = Q₈ + Q₈∙(0.35%) = Q₈∙(1 + 0.35%) = Q₀∙(1 + 0.35%)⁹</v>
-      </c>
-      <c r="J17" s="67"/>
-      <c r="K17" s="67"/>
-      <c r="L17" s="67"/>
-      <c r="M17" s="68"/>
+        <v>Q₉ = Q₈ + Q₈∙(-0.66%) = Q₈∙(1 + -0.66%) = Q₀∙(1 + -0.66%)⁹</v>
+      </c>
+      <c r="J17" s="63"/>
+      <c r="K17" s="63"/>
+      <c r="L17" s="63"/>
+      <c r="M17" s="64"/>
     </row>
     <row r="18" spans="1:13" ht="15.6" customHeight="1">
-      <c r="A18" s="5">
+      <c r="A18" s="4">
         <v>10</v>
       </c>
-      <c r="B18" s="9" t="s">
+      <c r="B18" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="C18" s="11">
+      <c r="C18" s="10">
         <f ca="1">C17*ROUND(1+SIGN(Sheet2!B$14-Sheet2!B$15)*Sheet2!D$15%,5)</f>
-        <v>1136.8143617416431</v>
-      </c>
-      <c r="D18" s="8">
+        <v>1245.216126804381</v>
+      </c>
+      <c r="D18" s="7">
         <f t="shared" ca="1" si="0"/>
-        <v>3.9423944461880183</v>
-      </c>
-      <c r="E18" s="6">
+        <v>-8.3235031428496313</v>
+      </c>
+      <c r="E18" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>3.4799999999999276E-3</v>
-      </c>
-      <c r="F18" s="92" t="str">
+        <v>-6.6399999999999793E-3</v>
+      </c>
+      <c r="F18" s="91" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>Q₁₀ = Q₉ + 3.94</v>
-      </c>
-      <c r="G18" s="93"/>
-      <c r="H18" s="93"/>
-      <c r="I18" s="66" t="str">
+        <v>Q₁₀ = Q₉ + -8.32</v>
+      </c>
+      <c r="G18" s="92"/>
+      <c r="H18" s="92"/>
+      <c r="I18" s="62" t="str">
         <f ca="1">B18&amp;" = "&amp;B17&amp;" + "&amp;B17&amp;"∙("&amp;ROUND(E18*100,2)&amp;"%) = "&amp;B17&amp;"∙(1 + "&amp;ROUND(E18*100,2)&amp;"%) = "&amp;B$8&amp;"∙(1 + "&amp;ROUND(E18*100,2)&amp;"%)¹⁰"</f>
-        <v>Q₁₀ = Q₉ + Q₉∙(0.35%) = Q₉∙(1 + 0.35%) = Q₀∙(1 + 0.35%)¹⁰</v>
-      </c>
-      <c r="J18" s="67"/>
-      <c r="K18" s="67"/>
-      <c r="L18" s="67"/>
-      <c r="M18" s="68"/>
+        <v>Q₁₀ = Q₉ + Q₉∙(-0.66%) = Q₉∙(1 + -0.66%) = Q₀∙(1 + -0.66%)¹⁰</v>
+      </c>
+      <c r="J18" s="63"/>
+      <c r="K18" s="63"/>
+      <c r="L18" s="63"/>
+      <c r="M18" s="64"/>
     </row>
     <row r="19" spans="1:13">
-      <c r="A19" s="5" t="s">
+      <c r="A19" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="B19" s="9" t="s">
+      <c r="B19" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="C19" s="10" t="s">
+      <c r="C19" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="D19" s="5" t="s">
+      <c r="D19" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="E19" s="5" t="s">
+      <c r="E19" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="F19" s="92" t="s">
+      <c r="F19" s="91" t="s">
         <v>42</v>
       </c>
-      <c r="G19" s="93"/>
-      <c r="H19" s="93"/>
-      <c r="I19" s="66" t="s">
+      <c r="G19" s="92"/>
+      <c r="H19" s="92"/>
+      <c r="I19" s="62" t="s">
         <v>42</v>
       </c>
-      <c r="J19" s="67"/>
-      <c r="K19" s="67"/>
-      <c r="L19" s="67"/>
-      <c r="M19" s="68"/>
+      <c r="J19" s="63"/>
+      <c r="K19" s="63"/>
+      <c r="L19" s="63"/>
+      <c r="M19" s="64"/>
     </row>
     <row r="20" spans="1:13" ht="15.75" thickBot="1">
-      <c r="A20" s="7" t="s">
+      <c r="A20" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B20" s="12" t="s">
+      <c r="B20" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="C20" s="13"/>
-      <c r="D20" s="14" t="s">
+      <c r="C20" s="12"/>
+      <c r="D20" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="E20" s="60">
+      <c r="E20" s="58">
         <f ca="1">E18</f>
-        <v>3.4799999999999276E-3</v>
-      </c>
-      <c r="F20" s="94" t="str">
+        <v>-6.6399999999999793E-3</v>
+      </c>
+      <c r="F20" s="103" t="str">
         <f>B20&amp;" = "&amp;B18&amp;" + "&amp;D20</f>
         <v>Qₙ = Q₁₀ + ???</v>
       </c>
-      <c r="G20" s="95"/>
-      <c r="H20" s="95"/>
-      <c r="I20" s="85" t="str">
+      <c r="G20" s="104"/>
+      <c r="H20" s="104"/>
+      <c r="I20" s="65" t="str">
         <f ca="1">B20&amp;" =  "&amp;B$8&amp;"∙(1 + "&amp;ROUND(E20*100,2)&amp;"%)ⁿ"</f>
-        <v>Qₙ =  Q₀∙(1 + 0.35%)ⁿ</v>
-      </c>
-      <c r="J20" s="86"/>
-      <c r="K20" s="86"/>
-      <c r="L20" s="86"/>
-      <c r="M20" s="87"/>
+        <v>Qₙ =  Q₀∙(1 + -0.66%)ⁿ</v>
+      </c>
+      <c r="J20" s="66"/>
+      <c r="K20" s="66"/>
+      <c r="L20" s="66"/>
+      <c r="M20" s="67"/>
     </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0"/>
@@ -3889,23 +4050,6 @@
     </customSheetView>
   </customSheetViews>
   <mergeCells count="33">
-    <mergeCell ref="M3:O4"/>
-    <mergeCell ref="I20:M20"/>
-    <mergeCell ref="I11:M11"/>
-    <mergeCell ref="I18:M18"/>
-    <mergeCell ref="I19:M19"/>
-    <mergeCell ref="E1:K1"/>
-    <mergeCell ref="F19:H19"/>
-    <mergeCell ref="E2:K4"/>
-    <mergeCell ref="E5:K6"/>
-    <mergeCell ref="I7:M7"/>
-    <mergeCell ref="F8:H8"/>
-    <mergeCell ref="I8:M8"/>
-    <mergeCell ref="F14:H14"/>
-    <mergeCell ref="F15:H15"/>
-    <mergeCell ref="I15:M15"/>
-    <mergeCell ref="F10:H10"/>
-    <mergeCell ref="F11:H11"/>
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="F7:H7"/>
     <mergeCell ref="F9:H9"/>
@@ -3922,6 +4066,23 @@
     <mergeCell ref="F13:H13"/>
     <mergeCell ref="I10:M10"/>
     <mergeCell ref="F12:H12"/>
+    <mergeCell ref="E1:K1"/>
+    <mergeCell ref="F19:H19"/>
+    <mergeCell ref="E2:K4"/>
+    <mergeCell ref="E5:K6"/>
+    <mergeCell ref="I7:M7"/>
+    <mergeCell ref="F8:H8"/>
+    <mergeCell ref="I8:M8"/>
+    <mergeCell ref="F14:H14"/>
+    <mergeCell ref="F15:H15"/>
+    <mergeCell ref="I15:M15"/>
+    <mergeCell ref="F10:H10"/>
+    <mergeCell ref="F11:H11"/>
+    <mergeCell ref="M3:O4"/>
+    <mergeCell ref="I20:M20"/>
+    <mergeCell ref="I11:M11"/>
+    <mergeCell ref="I18:M18"/>
+    <mergeCell ref="I19:M19"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="M3:O4" r:id="rId2" display="https://youtu.be/HoCMAoenzDw" xr:uid="{D9262481-9EDA-481F-B42B-0C6411D8AE1E}"/>
@@ -3932,7 +4093,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BBF79418-C12E-441C-955A-4392F0CF155C}">
   <dimension ref="A1:L36"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -3946,347 +4107,347 @@
   <sheetData>
     <row r="1" spans="1:12" ht="15.75" thickBot="1"/>
     <row r="2" spans="1:12" ht="18.75" thickBot="1">
-      <c r="F2" s="106" t="s">
-        <v>75</v>
-      </c>
-      <c r="G2" s="107"/>
-      <c r="H2" s="107"/>
-      <c r="I2" s="107"/>
-      <c r="J2" s="107"/>
-      <c r="K2" s="108"/>
+      <c r="F2" s="105" t="s">
+        <v>74</v>
+      </c>
+      <c r="G2" s="106"/>
+      <c r="H2" s="106"/>
+      <c r="I2" s="106"/>
+      <c r="J2" s="106"/>
+      <c r="K2" s="107"/>
     </row>
     <row r="3" spans="1:12" ht="15.75" thickBot="1"/>
     <row r="4" spans="1:12" ht="15" customHeight="1" thickTop="1">
-      <c r="A4" s="111" t="s">
+      <c r="A4" s="110" t="s">
         <v>50</v>
       </c>
-      <c r="B4" s="112"/>
-      <c r="C4" s="112"/>
-      <c r="D4" s="112"/>
-      <c r="E4" s="112"/>
-      <c r="F4" s="112"/>
-      <c r="G4" s="112"/>
-      <c r="H4" s="112"/>
-      <c r="I4" s="113"/>
-      <c r="K4" s="109" t="s">
+      <c r="B4" s="111"/>
+      <c r="C4" s="111"/>
+      <c r="D4" s="111"/>
+      <c r="E4" s="111"/>
+      <c r="F4" s="111"/>
+      <c r="G4" s="111"/>
+      <c r="H4" s="111"/>
+      <c r="I4" s="112"/>
+      <c r="K4" s="108" t="s">
         <v>52</v>
       </c>
-      <c r="L4" s="110"/>
+      <c r="L4" s="109"/>
     </row>
     <row r="5" spans="1:12" ht="15" customHeight="1">
-      <c r="A5" s="114"/>
-      <c r="B5" s="115"/>
-      <c r="C5" s="115"/>
-      <c r="D5" s="115"/>
-      <c r="E5" s="115"/>
-      <c r="F5" s="115"/>
-      <c r="G5" s="115"/>
-      <c r="H5" s="115"/>
-      <c r="I5" s="116"/>
-      <c r="K5" s="17" t="s">
+      <c r="A5" s="113"/>
+      <c r="B5" s="114"/>
+      <c r="C5" s="114"/>
+      <c r="D5" s="114"/>
+      <c r="E5" s="114"/>
+      <c r="F5" s="114"/>
+      <c r="G5" s="114"/>
+      <c r="H5" s="114"/>
+      <c r="I5" s="115"/>
+      <c r="K5" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="L5" s="18" t="s">
+      <c r="L5" s="17" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="15" customHeight="1">
-      <c r="A6" s="114"/>
-      <c r="B6" s="115"/>
-      <c r="C6" s="115"/>
-      <c r="D6" s="115"/>
-      <c r="E6" s="115"/>
-      <c r="F6" s="115"/>
-      <c r="G6" s="115"/>
-      <c r="H6" s="115"/>
-      <c r="I6" s="116"/>
-      <c r="K6" s="19" t="s">
+      <c r="A6" s="113"/>
+      <c r="B6" s="114"/>
+      <c r="C6" s="114"/>
+      <c r="D6" s="114"/>
+      <c r="E6" s="114"/>
+      <c r="F6" s="114"/>
+      <c r="G6" s="114"/>
+      <c r="H6" s="114"/>
+      <c r="I6" s="115"/>
+      <c r="K6" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="L6" s="20" t="s">
+      <c r="L6" s="19" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="15" customHeight="1" thickBot="1">
-      <c r="A7" s="117"/>
-      <c r="B7" s="118"/>
-      <c r="C7" s="118"/>
-      <c r="D7" s="118"/>
-      <c r="E7" s="118"/>
-      <c r="F7" s="118"/>
-      <c r="G7" s="118"/>
-      <c r="H7" s="118"/>
-      <c r="I7" s="119"/>
-      <c r="K7" s="21" t="s">
+      <c r="A7" s="116"/>
+      <c r="B7" s="117"/>
+      <c r="C7" s="117"/>
+      <c r="D7" s="117"/>
+      <c r="E7" s="117"/>
+      <c r="F7" s="117"/>
+      <c r="G7" s="117"/>
+      <c r="H7" s="117"/>
+      <c r="I7" s="118"/>
+      <c r="K7" s="20" t="s">
         <v>57</v>
       </c>
-      <c r="L7" s="20" t="s">
+      <c r="L7" s="19" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="15" customHeight="1">
-      <c r="A8" s="25"/>
-      <c r="B8" s="25"/>
-      <c r="C8" s="25"/>
-      <c r="D8" s="25"/>
-      <c r="E8" s="25"/>
-      <c r="F8" s="25"/>
-      <c r="G8" s="25"/>
-      <c r="H8" s="25"/>
-      <c r="I8" s="25"/>
-      <c r="K8" s="34" t="s">
+      <c r="A8" s="24"/>
+      <c r="B8" s="24"/>
+      <c r="C8" s="24"/>
+      <c r="D8" s="24"/>
+      <c r="E8" s="24"/>
+      <c r="F8" s="24"/>
+      <c r="G8" s="24"/>
+      <c r="H8" s="24"/>
+      <c r="I8" s="24"/>
+      <c r="K8" s="33" t="s">
         <v>59</v>
       </c>
-      <c r="L8" s="20" t="s">
+      <c r="L8" s="19" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="15" customHeight="1" thickBot="1">
-      <c r="K9" s="23" t="s">
+      <c r="K9" s="22" t="s">
         <v>61</v>
       </c>
-      <c r="L9" s="24" t="s">
+      <c r="L9" s="23" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="10" spans="1:12" s="15" customFormat="1" ht="30.6" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A10" s="53" t="s">
+    <row r="10" spans="1:12" s="14" customFormat="1" ht="30.6" customHeight="1" thickTop="1" thickBot="1">
+      <c r="A10" s="52" t="s">
         <v>72</v>
       </c>
-      <c r="B10" s="54" t="s">
+      <c r="B10" s="53" t="s">
         <v>65</v>
       </c>
-      <c r="C10" s="55" t="s">
+      <c r="C10" s="54" t="s">
         <v>1</v>
       </c>
-      <c r="D10" s="56" t="s">
+      <c r="D10" s="55" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="11" spans="1:12" s="2" customFormat="1" ht="15.75" thickBot="1">
-      <c r="A11" s="2">
+    <row r="11" spans="1:12" s="1" customFormat="1" ht="15.75" thickBot="1">
+      <c r="A11" s="1">
         <v>0</v>
       </c>
-      <c r="B11" s="45">
+      <c r="B11" s="44">
         <f ca="1">MOD(Sheet2!B28,1000)+1000</f>
-        <v>1066</v>
-      </c>
-      <c r="F11" s="111" t="s">
+        <v>1723</v>
+      </c>
+      <c r="F11" s="110" t="s">
         <v>49</v>
       </c>
-      <c r="G11" s="112"/>
-      <c r="H11" s="112"/>
-      <c r="I11" s="112"/>
-      <c r="J11" s="113"/>
-      <c r="K11" s="26" t="s">
+      <c r="G11" s="111"/>
+      <c r="H11" s="111"/>
+      <c r="I11" s="111"/>
+      <c r="J11" s="112"/>
+      <c r="K11" s="25" t="s">
         <v>63</v>
       </c>
-      <c r="L11" s="41"/>
+      <c r="L11" s="40"/>
     </row>
     <row r="12" spans="1:12" ht="15.75" thickBot="1">
       <c r="A12">
         <v>1</v>
       </c>
-      <c r="B12" s="46">
+      <c r="B12" s="45">
         <f ca="1">IF(Sheet2!C$28=0,B11*(1+SIGN(Sheet2!C$33-1/2)*Sheet2!D$28/10),B11+SIGN(Sheet2!C$33-1/2)*100*Sheet2!D$26)</f>
-        <v>1115.0123168945313</v>
-      </c>
-      <c r="C12" s="35"/>
-      <c r="D12" s="36"/>
-      <c r="F12" s="117"/>
-      <c r="G12" s="118"/>
-      <c r="H12" s="118"/>
-      <c r="I12" s="118"/>
-      <c r="J12" s="119"/>
-      <c r="K12" s="27" t="s">
+        <v>1656.2122802734375</v>
+      </c>
+      <c r="C12" s="34"/>
+      <c r="D12" s="35"/>
+      <c r="F12" s="116"/>
+      <c r="G12" s="117"/>
+      <c r="H12" s="117"/>
+      <c r="I12" s="117"/>
+      <c r="J12" s="118"/>
+      <c r="K12" s="26" t="s">
         <v>64</v>
       </c>
-      <c r="L12" s="42"/>
+      <c r="L12" s="41"/>
     </row>
     <row r="13" spans="1:12" ht="15.75" thickBot="1">
       <c r="A13">
         <v>2</v>
       </c>
-      <c r="B13" s="46">
+      <c r="B13" s="45">
         <f ca="1">IF(Sheet2!C$28=0,B12*(1+SIGN(Sheet2!C$33-1/2)*Sheet2!D$28/10),B12+SIGN(Sheet2!C$33-1/2)*100*Sheet2!D$26)</f>
-        <v>1166.2781114695222</v>
-      </c>
-      <c r="C13" s="37"/>
-      <c r="D13" s="38"/>
+        <v>1589.424560546875</v>
+      </c>
+      <c r="C13" s="36"/>
+      <c r="D13" s="37"/>
     </row>
     <row r="14" spans="1:12" ht="14.45" customHeight="1" thickBot="1">
       <c r="A14">
         <v>3</v>
       </c>
-      <c r="B14" s="46">
+      <c r="B14" s="45">
         <f ca="1">IF(Sheet2!C$28=0,B13*(1+SIGN(Sheet2!C$33-1/2)*Sheet2!D$28/10),B13+SIGN(Sheet2!C$33-1/2)*100*Sheet2!D$26)</f>
-        <v>1219.9009936332179</v>
-      </c>
-      <c r="C14" s="37"/>
-      <c r="D14" s="38"/>
-      <c r="F14" s="96" t="s">
+        <v>1522.6368408203125</v>
+      </c>
+      <c r="C14" s="36"/>
+      <c r="D14" s="37"/>
+      <c r="F14" s="93" t="s">
         <v>67</v>
       </c>
-      <c r="G14" s="97"/>
-      <c r="H14" s="97"/>
-      <c r="I14" s="97"/>
-      <c r="J14" s="98"/>
-      <c r="K14" s="28" t="s">
-        <v>83</v>
-      </c>
-      <c r="L14" s="43"/>
+      <c r="G14" s="94"/>
+      <c r="H14" s="94"/>
+      <c r="I14" s="94"/>
+      <c r="J14" s="95"/>
+      <c r="K14" s="27" t="s">
+        <v>82</v>
+      </c>
+      <c r="L14" s="42"/>
     </row>
     <row r="15" spans="1:12">
       <c r="A15">
         <v>4</v>
       </c>
-      <c r="B15" s="46">
+      <c r="B15" s="45">
         <f ca="1">IF(Sheet2!C$28=0,B14*(1+SIGN(Sheet2!C$33-1/2)*Sheet2!D$28/10),B14+SIGN(Sheet2!C$33-1/2)*100*Sheet2!D$26)</f>
-        <v>1275.9893370477628</v>
-      </c>
-      <c r="C15" s="37"/>
-      <c r="D15" s="38"/>
-      <c r="F15" s="99"/>
-      <c r="G15" s="100"/>
-      <c r="H15" s="100"/>
-      <c r="I15" s="100"/>
-      <c r="J15" s="101"/>
+        <v>1455.84912109375</v>
+      </c>
+      <c r="C15" s="36"/>
+      <c r="D15" s="37"/>
+      <c r="F15" s="96"/>
+      <c r="G15" s="97"/>
+      <c r="H15" s="97"/>
+      <c r="I15" s="97"/>
+      <c r="J15" s="98"/>
     </row>
     <row r="16" spans="1:12" ht="15.75" thickBot="1">
       <c r="A16">
         <v>5</v>
       </c>
-      <c r="B16" s="46">
+      <c r="B16" s="45">
         <f ca="1">IF(Sheet2!C$28=0,B15*(1+SIGN(Sheet2!C$33-1/2)*Sheet2!D$28/10),B15+SIGN(Sheet2!C$33-1/2)*100*Sheet2!D$26)</f>
-        <v>1334.6564981560439</v>
-      </c>
-      <c r="C16" s="37"/>
-      <c r="D16" s="38"/>
-      <c r="F16" s="102"/>
-      <c r="G16" s="103"/>
-      <c r="H16" s="103"/>
-      <c r="I16" s="103"/>
-      <c r="J16" s="104"/>
+        <v>1389.0614013671875</v>
+      </c>
+      <c r="C16" s="36"/>
+      <c r="D16" s="37"/>
+      <c r="F16" s="99"/>
+      <c r="G16" s="100"/>
+      <c r="H16" s="100"/>
+      <c r="I16" s="100"/>
+      <c r="J16" s="101"/>
     </row>
     <row r="17" spans="1:11" ht="15.75" thickBot="1">
       <c r="A17">
         <v>6</v>
       </c>
-      <c r="B17" s="46">
+      <c r="B17" s="45">
         <f ca="1">IF(Sheet2!C$28=0,B16*(1+SIGN(Sheet2!C$33-1/2)*Sheet2!D$28/10),B16+SIGN(Sheet2!C$33-1/2)*100*Sheet2!D$26)</f>
-        <v>1396.0210452789045</v>
-      </c>
-      <c r="C17" s="37"/>
-      <c r="D17" s="38"/>
+        <v>1322.273681640625</v>
+      </c>
+      <c r="C17" s="36"/>
+      <c r="D17" s="37"/>
     </row>
     <row r="18" spans="1:11" ht="15.75" thickBot="1">
       <c r="A18">
         <v>7</v>
       </c>
-      <c r="B18" s="46">
+      <c r="B18" s="45">
         <f ca="1">IF(Sheet2!C$28=0,B17*(1+SIGN(Sheet2!C$33-1/2)*Sheet2!D$28/10),B17+SIGN(Sheet2!C$33-1/2)*100*Sheet2!D$26)</f>
-        <v>1460.2069982457379</v>
-      </c>
-      <c r="C18" s="37"/>
-      <c r="D18" s="38"/>
-      <c r="F18" s="64" t="s">
+        <v>1255.4859619140625</v>
+      </c>
+      <c r="C18" s="36"/>
+      <c r="D18" s="37"/>
+      <c r="F18" s="68" t="s">
         <v>71</v>
       </c>
-      <c r="G18" s="72"/>
-      <c r="H18" s="72"/>
-      <c r="I18" s="72"/>
-      <c r="J18" s="65"/>
-      <c r="K18" s="44"/>
+      <c r="G18" s="69"/>
+      <c r="H18" s="69"/>
+      <c r="I18" s="69"/>
+      <c r="J18" s="70"/>
+      <c r="K18" s="43"/>
     </row>
     <row r="19" spans="1:11" ht="15.75" thickBot="1">
       <c r="A19">
         <v>8</v>
       </c>
-      <c r="B19" s="46">
+      <c r="B19" s="45">
         <f ca="1">IF(Sheet2!C$28=0,B18*(1+SIGN(Sheet2!C$33-1/2)*Sheet2!D$28/10),B18+SIGN(Sheet2!C$33-1/2)*100*Sheet2!D$26)</f>
-        <v>1527.3440790427662</v>
-      </c>
-      <c r="C19" s="37"/>
-      <c r="D19" s="38"/>
-      <c r="F19" s="64" t="s">
+        <v>1188.6982421875</v>
+      </c>
+      <c r="C19" s="36"/>
+      <c r="D19" s="37"/>
+      <c r="F19" s="68" t="s">
         <v>70</v>
       </c>
-      <c r="G19" s="72"/>
-      <c r="H19" s="72"/>
-      <c r="I19" s="72"/>
-      <c r="J19" s="65"/>
-      <c r="K19" s="42"/>
+      <c r="G19" s="69"/>
+      <c r="H19" s="69"/>
+      <c r="I19" s="69"/>
+      <c r="J19" s="70"/>
+      <c r="K19" s="41"/>
     </row>
     <row r="20" spans="1:11" ht="15.75" thickBot="1">
       <c r="A20">
         <v>9</v>
       </c>
-      <c r="B20" s="46">
+      <c r="B20" s="45">
         <f ca="1">IF(Sheet2!C$28=0,B19*(1+SIGN(Sheet2!C$33-1/2)*Sheet2!D$28/10),B19+SIGN(Sheet2!C$33-1/2)*100*Sheet2!D$26)</f>
-        <v>1597.5679739855711</v>
-      </c>
-      <c r="C20" s="37"/>
-      <c r="D20" s="38"/>
-      <c r="F20" s="64" t="s">
+        <v>1121.9105224609375</v>
+      </c>
+      <c r="C20" s="36"/>
+      <c r="D20" s="37"/>
+      <c r="F20" s="68" t="s">
         <v>66</v>
       </c>
-      <c r="G20" s="72"/>
-      <c r="H20" s="72"/>
-      <c r="I20" s="72"/>
-      <c r="J20" s="65"/>
-      <c r="K20" s="42"/>
+      <c r="G20" s="69"/>
+      <c r="H20" s="69"/>
+      <c r="I20" s="69"/>
+      <c r="J20" s="70"/>
+      <c r="K20" s="41"/>
     </row>
     <row r="21" spans="1:11">
       <c r="A21">
         <v>10</v>
       </c>
-      <c r="B21" s="46">
+      <c r="B21" s="45">
         <f ca="1">IF(Sheet2!C$28=0,B20*(1+SIGN(Sheet2!C$33-1/2)*Sheet2!D$28/10),B20+SIGN(Sheet2!C$33-1/2)*100*Sheet2!D$26)</f>
-        <v>1671.0206079457353</v>
-      </c>
-      <c r="C21" s="37"/>
-      <c r="D21" s="38"/>
+        <v>1055.122802734375</v>
+      </c>
+      <c r="C21" s="36"/>
+      <c r="D21" s="37"/>
     </row>
     <row r="22" spans="1:11">
       <c r="A22">
         <v>11</v>
       </c>
-      <c r="B22" s="46">
+      <c r="B22" s="45">
         <f ca="1">IF(Sheet2!C$28=0,B21*(1+SIGN(Sheet2!C$33-1/2)*Sheet2!D$28/10),B21+SIGN(Sheet2!C$33-1/2)*100*Sheet2!D$26)</f>
-        <v>1747.8504311858183</v>
-      </c>
-      <c r="C22" s="37"/>
-      <c r="D22" s="38"/>
+        <v>988.3350830078125</v>
+      </c>
+      <c r="C22" s="36"/>
+      <c r="D22" s="37"/>
     </row>
     <row r="23" spans="1:11" ht="15.75" thickBot="1">
       <c r="A23">
         <v>12</v>
       </c>
-      <c r="B23" s="46">
+      <c r="B23" s="45">
         <f ca="1">IF(Sheet2!C$28=0,B22*(1+SIGN(Sheet2!C$33-1/2)*Sheet2!D$28/10),B22+SIGN(Sheet2!C$33-1/2)*100*Sheet2!D$26)</f>
-        <v>1828.2127193823683</v>
-      </c>
-      <c r="C23" s="39"/>
-      <c r="D23" s="40"/>
+        <v>921.54736328125</v>
+      </c>
+      <c r="C23" s="38"/>
+      <c r="D23" s="39"/>
     </row>
     <row r="35" spans="2:5" hidden="1">
-      <c r="B35" s="58" t="s">
+      <c r="B35" s="56" t="s">
+        <v>80</v>
+      </c>
+      <c r="C35" s="56"/>
+      <c r="D35" s="56"/>
+      <c r="E35" s="56" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="36" spans="2:5">
+      <c r="B36" s="56" t="s">
         <v>81</v>
       </c>
-      <c r="C35" s="58"/>
-      <c r="D35" s="58"/>
-      <c r="E35" s="58" t="s">
+      <c r="C36" s="56"/>
+      <c r="D36" s="56"/>
+      <c r="E36" s="56" t="s">
         <v>79</v>
-      </c>
-    </row>
-    <row r="36" spans="2:5">
-      <c r="B36" s="58" t="s">
-        <v>82</v>
-      </c>
-      <c r="C36" s="58"/>
-      <c r="D36" s="58"/>
-      <c r="E36" s="58" t="s">
-        <v>80</v>
       </c>
     </row>
   </sheetData>
@@ -4344,7 +4505,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77757405-FFA4-43AF-9C54-9F380FA82D70}">
   <dimension ref="A1:L39"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -4359,348 +4520,348 @@
   <sheetData>
     <row r="1" spans="1:12" ht="15.75" thickBot="1"/>
     <row r="2" spans="1:12" ht="18.75" thickBot="1">
-      <c r="F2" s="106" t="s">
-        <v>75</v>
-      </c>
-      <c r="G2" s="107"/>
-      <c r="H2" s="107"/>
-      <c r="I2" s="107"/>
-      <c r="J2" s="107"/>
-      <c r="K2" s="108"/>
+      <c r="F2" s="105" t="s">
+        <v>74</v>
+      </c>
+      <c r="G2" s="106"/>
+      <c r="H2" s="106"/>
+      <c r="I2" s="106"/>
+      <c r="J2" s="106"/>
+      <c r="K2" s="107"/>
     </row>
     <row r="3" spans="1:12" ht="15.75" thickBot="1"/>
     <row r="4" spans="1:12" ht="15" customHeight="1" thickTop="1">
-      <c r="A4" s="111" t="s">
+      <c r="A4" s="110" t="s">
         <v>51</v>
       </c>
-      <c r="B4" s="112"/>
-      <c r="C4" s="112"/>
-      <c r="D4" s="112"/>
-      <c r="E4" s="112"/>
-      <c r="F4" s="112"/>
-      <c r="G4" s="112"/>
-      <c r="H4" s="112"/>
-      <c r="I4" s="113"/>
-      <c r="K4" s="120" t="s">
+      <c r="B4" s="111"/>
+      <c r="C4" s="111"/>
+      <c r="D4" s="111"/>
+      <c r="E4" s="111"/>
+      <c r="F4" s="111"/>
+      <c r="G4" s="111"/>
+      <c r="H4" s="111"/>
+      <c r="I4" s="112"/>
+      <c r="K4" s="119" t="s">
         <v>52</v>
       </c>
-      <c r="L4" s="121"/>
+      <c r="L4" s="120"/>
     </row>
     <row r="5" spans="1:12" ht="15" customHeight="1">
-      <c r="A5" s="114"/>
-      <c r="B5" s="115"/>
-      <c r="C5" s="115"/>
-      <c r="D5" s="115"/>
-      <c r="E5" s="115"/>
-      <c r="F5" s="115"/>
-      <c r="G5" s="115"/>
-      <c r="H5" s="115"/>
-      <c r="I5" s="116"/>
-      <c r="K5" s="17" t="s">
+      <c r="A5" s="113"/>
+      <c r="B5" s="114"/>
+      <c r="C5" s="114"/>
+      <c r="D5" s="114"/>
+      <c r="E5" s="114"/>
+      <c r="F5" s="114"/>
+      <c r="G5" s="114"/>
+      <c r="H5" s="114"/>
+      <c r="I5" s="115"/>
+      <c r="K5" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="L5" s="18" t="s">
+      <c r="L5" s="17" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="15" customHeight="1">
-      <c r="A6" s="114"/>
-      <c r="B6" s="115"/>
-      <c r="C6" s="115"/>
-      <c r="D6" s="115"/>
-      <c r="E6" s="115"/>
-      <c r="F6" s="115"/>
-      <c r="G6" s="115"/>
-      <c r="H6" s="115"/>
-      <c r="I6" s="116"/>
-      <c r="K6" s="19" t="s">
+      <c r="A6" s="113"/>
+      <c r="B6" s="114"/>
+      <c r="C6" s="114"/>
+      <c r="D6" s="114"/>
+      <c r="E6" s="114"/>
+      <c r="F6" s="114"/>
+      <c r="G6" s="114"/>
+      <c r="H6" s="114"/>
+      <c r="I6" s="115"/>
+      <c r="K6" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="L6" s="20" t="s">
+      <c r="L6" s="19" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="15" customHeight="1" thickBot="1">
-      <c r="A7" s="117"/>
-      <c r="B7" s="118"/>
-      <c r="C7" s="118"/>
-      <c r="D7" s="118"/>
-      <c r="E7" s="118"/>
-      <c r="F7" s="118"/>
-      <c r="G7" s="118"/>
-      <c r="H7" s="118"/>
-      <c r="I7" s="119"/>
-      <c r="K7" s="21" t="s">
+      <c r="A7" s="116"/>
+      <c r="B7" s="117"/>
+      <c r="C7" s="117"/>
+      <c r="D7" s="117"/>
+      <c r="E7" s="117"/>
+      <c r="F7" s="117"/>
+      <c r="G7" s="117"/>
+      <c r="H7" s="117"/>
+      <c r="I7" s="118"/>
+      <c r="K7" s="20" t="s">
         <v>57</v>
       </c>
-      <c r="L7" s="20" t="s">
+      <c r="L7" s="19" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="15" customHeight="1">
-      <c r="A8" s="25"/>
-      <c r="B8" s="25"/>
-      <c r="C8" s="25"/>
-      <c r="D8" s="25"/>
-      <c r="E8" s="25"/>
-      <c r="F8" s="25"/>
-      <c r="G8" s="25"/>
-      <c r="H8" s="25"/>
-      <c r="I8" s="25"/>
-      <c r="K8" s="22" t="s">
+      <c r="A8" s="24"/>
+      <c r="B8" s="24"/>
+      <c r="C8" s="24"/>
+      <c r="D8" s="24"/>
+      <c r="E8" s="24"/>
+      <c r="F8" s="24"/>
+      <c r="G8" s="24"/>
+      <c r="H8" s="24"/>
+      <c r="I8" s="24"/>
+      <c r="K8" s="21" t="s">
         <v>59</v>
       </c>
-      <c r="L8" s="20" t="s">
+      <c r="L8" s="19" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="15" customHeight="1" thickBot="1">
-      <c r="K9" s="23" t="s">
+      <c r="K9" s="22" t="s">
         <v>61</v>
       </c>
-      <c r="L9" s="24" t="s">
+      <c r="L9" s="23" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="10" spans="1:12" s="15" customFormat="1" ht="30.6" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A10" s="29" t="s">
+    <row r="10" spans="1:12" s="14" customFormat="1" ht="30.6" customHeight="1" thickTop="1" thickBot="1">
+      <c r="A10" s="28" t="s">
         <v>73</v>
       </c>
-      <c r="B10" s="30" t="s">
+      <c r="B10" s="29" t="s">
         <v>47</v>
       </c>
-      <c r="C10" s="31" t="s">
+      <c r="C10" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="D10" s="32" t="s">
+      <c r="D10" s="31" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="11" spans="1:12" s="2" customFormat="1" ht="15.75" thickBot="1">
-      <c r="A11" s="2">
+    <row r="11" spans="1:12" s="1" customFormat="1" ht="15.75" thickBot="1">
+      <c r="A11" s="1">
         <v>0</v>
       </c>
-      <c r="B11" s="45">
+      <c r="B11" s="44">
         <f ca="1">MOD(Sheet2!B28,1000)+1000</f>
-        <v>1066</v>
-      </c>
-      <c r="F11" s="111" t="s">
+        <v>1723</v>
+      </c>
+      <c r="F11" s="110" t="s">
         <v>49</v>
       </c>
-      <c r="G11" s="112"/>
-      <c r="H11" s="112"/>
-      <c r="I11" s="112"/>
-      <c r="J11" s="113"/>
-      <c r="K11" s="26" t="s">
+      <c r="G11" s="111"/>
+      <c r="H11" s="111"/>
+      <c r="I11" s="111"/>
+      <c r="J11" s="112"/>
+      <c r="K11" s="25" t="s">
         <v>63</v>
       </c>
-      <c r="L11" s="41"/>
+      <c r="L11" s="40"/>
     </row>
     <row r="12" spans="1:12" ht="15.75" thickBot="1">
       <c r="A12">
         <v>1</v>
       </c>
-      <c r="B12" s="46">
+      <c r="B12" s="45">
         <f ca="1">IF(Sheet2!C$28=1,B11*(1+SIGN(Sheet2!C$33-1/2)*Sheet2!D$28%),B11+SIGN(Sheet2!C$33-1/2)*100*Sheet2!D$26)</f>
-        <v>1139.42529296875</v>
-      </c>
-      <c r="C12" s="47"/>
-      <c r="D12" s="48"/>
-      <c r="F12" s="117"/>
-      <c r="G12" s="118"/>
-      <c r="H12" s="118"/>
-      <c r="I12" s="118"/>
-      <c r="J12" s="119"/>
-      <c r="K12" s="27" t="s">
+        <v>1711.0518405151367</v>
+      </c>
+      <c r="C12" s="46"/>
+      <c r="D12" s="47"/>
+      <c r="F12" s="116"/>
+      <c r="G12" s="117"/>
+      <c r="H12" s="117"/>
+      <c r="I12" s="117"/>
+      <c r="J12" s="118"/>
+      <c r="K12" s="26" t="s">
         <v>64</v>
       </c>
-      <c r="L12" s="42"/>
+      <c r="L12" s="41"/>
     </row>
     <row r="13" spans="1:12" ht="15.75" thickBot="1">
       <c r="A13">
         <v>2</v>
       </c>
-      <c r="B13" s="46">
+      <c r="B13" s="45">
         <f ca="1">IF(Sheet2!C$28=1,B12*(1+SIGN(Sheet2!C$33-1/2)*Sheet2!D$28%),B12+SIGN(Sheet2!C$33-1/2)*100*Sheet2!D$26)</f>
-        <v>1212.8505859375</v>
-      </c>
-      <c r="C13" s="49"/>
-      <c r="D13" s="50"/>
+        <v>1699.1865356530684</v>
+      </c>
+      <c r="C13" s="48"/>
+      <c r="D13" s="49"/>
     </row>
     <row r="14" spans="1:12" ht="14.45" customHeight="1" thickBot="1">
       <c r="A14">
         <v>3</v>
       </c>
-      <c r="B14" s="46">
+      <c r="B14" s="45">
         <f ca="1">IF(Sheet2!C$28=1,B13*(1+SIGN(Sheet2!C$33-1/2)*Sheet2!D$28%),B13+SIGN(Sheet2!C$33-1/2)*100*Sheet2!D$26)</f>
-        <v>1286.27587890625</v>
-      </c>
-      <c r="C14" s="49"/>
-      <c r="D14" s="50"/>
-      <c r="E14" s="16"/>
-      <c r="F14" s="96" t="s">
+        <v>1687.4035108576447</v>
+      </c>
+      <c r="C14" s="48"/>
+      <c r="D14" s="49"/>
+      <c r="E14" s="15"/>
+      <c r="F14" s="93" t="s">
         <v>67</v>
       </c>
-      <c r="G14" s="97"/>
-      <c r="H14" s="97"/>
-      <c r="I14" s="97"/>
-      <c r="J14" s="98"/>
-      <c r="K14" s="27" t="s">
-        <v>83</v>
-      </c>
-      <c r="L14" s="43"/>
+      <c r="G14" s="94"/>
+      <c r="H14" s="94"/>
+      <c r="I14" s="94"/>
+      <c r="J14" s="95"/>
+      <c r="K14" s="26" t="s">
+        <v>82</v>
+      </c>
+      <c r="L14" s="42"/>
     </row>
     <row r="15" spans="1:12">
       <c r="A15">
         <v>4</v>
       </c>
-      <c r="B15" s="46">
+      <c r="B15" s="45">
         <f ca="1">IF(Sheet2!C$28=1,B14*(1+SIGN(Sheet2!C$33-1/2)*Sheet2!D$28%),B14+SIGN(Sheet2!C$33-1/2)*100*Sheet2!D$26)</f>
-        <v>1359.701171875</v>
-      </c>
-      <c r="C15" s="49"/>
-      <c r="D15" s="50"/>
-      <c r="F15" s="99"/>
-      <c r="G15" s="100"/>
-      <c r="H15" s="100"/>
-      <c r="I15" s="100"/>
-      <c r="J15" s="101"/>
+        <v>1675.7021955569801</v>
+      </c>
+      <c r="C15" s="48"/>
+      <c r="D15" s="49"/>
+      <c r="F15" s="96"/>
+      <c r="G15" s="97"/>
+      <c r="H15" s="97"/>
+      <c r="I15" s="97"/>
+      <c r="J15" s="98"/>
     </row>
     <row r="16" spans="1:12" ht="15.75" thickBot="1">
       <c r="A16">
         <v>5</v>
       </c>
-      <c r="B16" s="46">
+      <c r="B16" s="45">
         <f ca="1">IF(Sheet2!C$28=1,B15*(1+SIGN(Sheet2!C$33-1/2)*Sheet2!D$28%),B15+SIGN(Sheet2!C$33-1/2)*100*Sheet2!D$26)</f>
-        <v>1433.12646484375</v>
-      </c>
-      <c r="C16" s="49"/>
-      <c r="D16" s="50"/>
-      <c r="F16" s="102"/>
-      <c r="G16" s="103"/>
-      <c r="H16" s="103"/>
-      <c r="I16" s="103"/>
-      <c r="J16" s="104"/>
+        <v>1664.082023135825</v>
+      </c>
+      <c r="C16" s="48"/>
+      <c r="D16" s="49"/>
+      <c r="F16" s="99"/>
+      <c r="G16" s="100"/>
+      <c r="H16" s="100"/>
+      <c r="I16" s="100"/>
+      <c r="J16" s="101"/>
     </row>
     <row r="17" spans="1:11" ht="15.75" thickBot="1">
       <c r="A17">
         <v>6</v>
       </c>
-      <c r="B17" s="46">
+      <c r="B17" s="45">
         <f ca="1">IF(Sheet2!C$28=1,B16*(1+SIGN(Sheet2!C$33-1/2)*Sheet2!D$28%),B16+SIGN(Sheet2!C$33-1/2)*100*Sheet2!D$26)</f>
-        <v>1506.5517578125</v>
-      </c>
-      <c r="C17" s="49"/>
-      <c r="D17" s="50"/>
+        <v>1652.5424309081286</v>
+      </c>
+      <c r="C17" s="48"/>
+      <c r="D17" s="49"/>
     </row>
     <row r="18" spans="1:11" ht="15.75" thickBot="1">
       <c r="A18">
         <v>7</v>
       </c>
-      <c r="B18" s="46">
+      <c r="B18" s="45">
         <f ca="1">IF(Sheet2!C$28=1,B17*(1+SIGN(Sheet2!C$33-1/2)*Sheet2!D$28%),B17+SIGN(Sheet2!C$33-1/2)*100*Sheet2!D$26)</f>
-        <v>1579.97705078125</v>
-      </c>
-      <c r="C18" s="49"/>
-      <c r="D18" s="50"/>
-      <c r="F18" s="64" t="s">
+        <v>1641.0828600897921</v>
+      </c>
+      <c r="C18" s="48"/>
+      <c r="D18" s="49"/>
+      <c r="F18" s="68" t="s">
         <v>71</v>
       </c>
-      <c r="G18" s="72"/>
-      <c r="H18" s="72"/>
-      <c r="I18" s="72"/>
-      <c r="J18" s="65"/>
-      <c r="K18" s="44"/>
+      <c r="G18" s="69"/>
+      <c r="H18" s="69"/>
+      <c r="I18" s="69"/>
+      <c r="J18" s="70"/>
+      <c r="K18" s="43"/>
     </row>
     <row r="19" spans="1:11" ht="15.75" thickBot="1">
       <c r="A19">
         <v>8</v>
       </c>
-      <c r="B19" s="46">
+      <c r="B19" s="45">
         <f ca="1">IF(Sheet2!C$28=1,B18*(1+SIGN(Sheet2!C$33-1/2)*Sheet2!D$28%),B18+SIGN(Sheet2!C$33-1/2)*100*Sheet2!D$26)</f>
-        <v>1653.40234375</v>
-      </c>
-      <c r="C19" s="49"/>
-      <c r="D19" s="50"/>
-      <c r="F19" s="64" t="s">
+        <v>1629.7027557716096</v>
+      </c>
+      <c r="C19" s="48"/>
+      <c r="D19" s="49"/>
+      <c r="F19" s="68" t="s">
         <v>68</v>
       </c>
-      <c r="G19" s="72"/>
-      <c r="H19" s="72"/>
-      <c r="I19" s="72"/>
-      <c r="J19" s="65"/>
-      <c r="K19" s="42"/>
+      <c r="G19" s="69"/>
+      <c r="H19" s="69"/>
+      <c r="I19" s="69"/>
+      <c r="J19" s="70"/>
+      <c r="K19" s="41"/>
     </row>
     <row r="20" spans="1:11" ht="15.75" thickBot="1">
       <c r="A20">
         <v>9</v>
       </c>
-      <c r="B20" s="46">
+      <c r="B20" s="45">
         <f ca="1">IF(Sheet2!C$28=1,B19*(1+SIGN(Sheet2!C$33-1/2)*Sheet2!D$28%),B19+SIGN(Sheet2!C$33-1/2)*100*Sheet2!D$26)</f>
-        <v>1726.82763671875</v>
-      </c>
-      <c r="C20" s="49"/>
-      <c r="D20" s="50"/>
-      <c r="F20" s="64" t="s">
+        <v>1618.4015668923987</v>
+      </c>
+      <c r="C20" s="48"/>
+      <c r="D20" s="49"/>
+      <c r="F20" s="68" t="s">
         <v>69</v>
       </c>
-      <c r="G20" s="72"/>
-      <c r="H20" s="72"/>
-      <c r="I20" s="72"/>
-      <c r="J20" s="65"/>
-      <c r="K20" s="42"/>
+      <c r="G20" s="69"/>
+      <c r="H20" s="69"/>
+      <c r="I20" s="69"/>
+      <c r="J20" s="70"/>
+      <c r="K20" s="41"/>
     </row>
     <row r="21" spans="1:11">
       <c r="A21">
         <v>10</v>
       </c>
-      <c r="B21" s="46">
+      <c r="B21" s="45">
         <f ca="1">IF(Sheet2!C$28=1,B20*(1+SIGN(Sheet2!C$33-1/2)*Sheet2!D$28%),B20+SIGN(Sheet2!C$33-1/2)*100*Sheet2!D$26)</f>
-        <v>1800.2529296875</v>
-      </c>
-      <c r="C21" s="49"/>
-      <c r="D21" s="50"/>
+        <v>1607.1787462123157</v>
+      </c>
+      <c r="C21" s="48"/>
+      <c r="D21" s="49"/>
     </row>
     <row r="22" spans="1:11">
       <c r="A22">
         <v>11</v>
       </c>
-      <c r="B22" s="46">
+      <c r="B22" s="45">
         <f ca="1">IF(Sheet2!C$28=1,B21*(1+SIGN(Sheet2!C$33-1/2)*Sheet2!D$28%),B21+SIGN(Sheet2!C$33-1/2)*100*Sheet2!D$26)</f>
-        <v>1873.67822265625</v>
-      </c>
-      <c r="C22" s="49"/>
-      <c r="D22" s="50"/>
+        <v>1596.0337502863567</v>
+      </c>
+      <c r="C22" s="48"/>
+      <c r="D22" s="49"/>
     </row>
     <row r="23" spans="1:11" ht="15.75" thickBot="1">
       <c r="A23">
         <v>12</v>
       </c>
-      <c r="B23" s="46">
+      <c r="B23" s="45">
         <f ca="1">IF(Sheet2!C$28=1,B22*(1+SIGN(Sheet2!C$33-1/2)*Sheet2!D$28%),B22+SIGN(Sheet2!C$33-1/2)*100*Sheet2!D$26)</f>
-        <v>1947.103515625</v>
-      </c>
-      <c r="C23" s="51"/>
-      <c r="D23" s="52"/>
+        <v>1584.9660394380423</v>
+      </c>
+      <c r="C23" s="50"/>
+      <c r="D23" s="51"/>
     </row>
     <row r="38" spans="2:5" hidden="1">
-      <c r="B38" s="57" t="s">
+      <c r="B38" s="56" t="s">
+        <v>80</v>
+      </c>
+      <c r="C38" s="56"/>
+      <c r="D38" s="56"/>
+      <c r="E38" s="56" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="39" spans="2:5" hidden="1">
+      <c r="B39" s="56" t="s">
         <v>81</v>
       </c>
-      <c r="C38" s="57"/>
-      <c r="D38" s="57"/>
-      <c r="E38" s="57" t="s">
+      <c r="C39" s="56"/>
+      <c r="D39" s="56"/>
+      <c r="E39" s="56" t="s">
         <v>79</v>
-      </c>
-    </row>
-    <row r="39" spans="2:5" hidden="1">
-      <c r="B39" s="57" t="s">
-        <v>82</v>
-      </c>
-      <c r="C39" s="57"/>
-      <c r="D39" s="57"/>
-      <c r="E39" s="57" t="s">
-        <v>80</v>
       </c>
     </row>
   </sheetData>
@@ -4757,7 +4918,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73B50B47-7081-4CB7-870D-CE3CF3EB27FC}">
   <dimension ref="A1:W45"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -5033,19 +5194,19 @@
       </c>
       <c r="B6">
         <f>CODE(MID('Constant Change'!D$1,Sheet2!A6,1))</f>
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="C6">
         <f>MOD(B6,16)</f>
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D6">
         <f>MOD((B6-C6)/16,16)</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E6">
         <f ca="1">INDIRECT("R"&amp;(C6+1)&amp;"C"&amp;(D6+7),0)</f>
-        <v>13</v>
+        <v>439</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -5105,19 +5266,19 @@
       </c>
       <c r="B7">
         <f>CODE(MID('Constant Change'!D$1,Sheet2!A7,1))</f>
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="C7">
         <f t="shared" ref="C7:C10" si="0">MOD(B7,16)</f>
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="D7">
         <f t="shared" ref="D7:D10" si="1">MOD((B7-C7)/16,16)</f>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E7">
         <f t="shared" ref="E7:E10" ca="1" si="2">INDIRECT("R"&amp;(C7+1)&amp;"C"&amp;(D7+7),0)</f>
-        <v>331</v>
+        <v>839</v>
       </c>
       <c r="G7">
         <v>6</v>
@@ -5177,19 +5338,19 @@
       </c>
       <c r="B8">
         <f>CODE(MID('Constant Change'!D$1,Sheet2!A8,1))</f>
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="C8">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="D8">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E8">
         <f t="shared" ca="1" si="2"/>
-        <v>839</v>
+        <v>211</v>
       </c>
       <c r="G8">
         <v>7</v>
@@ -5321,19 +5482,19 @@
       </c>
       <c r="B10">
         <f>CODE(MID('Constant Change'!D$1,Sheet2!A10,1))</f>
-        <v>100</v>
+        <v>32</v>
       </c>
       <c r="C10">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D10">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E10">
         <f t="shared" ca="1" si="2"/>
-        <v>151</v>
+        <v>2</v>
       </c>
       <c r="G10">
         <v>9</v>
@@ -5393,7 +5554,7 @@
       </c>
       <c r="B11">
         <f ca="1">MOD(PRODUCT(E6:E10),F13)</f>
-        <v>25621</v>
+        <v>3778</v>
       </c>
       <c r="F11">
         <v>1103515245</v>
@@ -5456,19 +5617,19 @@
       </c>
       <c r="B12">
         <f ca="1">MOD(B11*F11+F12,F13)</f>
-        <v>13098</v>
+        <v>5331</v>
       </c>
       <c r="C12">
         <f ca="1">MOD(B12,2)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D12">
         <f ca="1">B12/F$13</f>
-        <v>0.39971923828125</v>
+        <v>0.162689208984375</v>
       </c>
       <c r="E12">
         <f ca="1">IF(D12&lt;0.25,0,IF(D12&lt;0.5,1,IF(D12&lt;0.75,3,4)))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F12">
         <v>12345</v>
@@ -5529,9 +5690,9 @@
       <c r="A13" t="s">
         <v>5</v>
       </c>
-      <c r="B13" s="3">
+      <c r="B13" s="2">
         <f t="shared" ref="B13:B33" ca="1" si="3">MOD(B12*F$11+F$12,F$13)</f>
-        <v>17691</v>
+        <v>22544</v>
       </c>
       <c r="C13">
         <f t="shared" ref="C13:C33" ca="1" si="4">IF(D13&lt;0.5,0,1)</f>
@@ -5539,7 +5700,7 @@
       </c>
       <c r="D13">
         <f t="shared" ref="D13:D33" ca="1" si="5">B13/F$13</f>
-        <v>0.539886474609375</v>
+        <v>0.68798828125</v>
       </c>
       <c r="E13">
         <f t="shared" ref="E13:E33" ca="1" si="6">IF(D13&lt;0.25,0,IF(D13&lt;0.5,1,IF(D13&lt;0.75,3,4)))</f>
@@ -5604,21 +5765,21 @@
       <c r="A14" t="s">
         <v>6</v>
       </c>
-      <c r="B14" s="3">
+      <c r="B14" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>22200</v>
+        <v>3849</v>
       </c>
       <c r="C14">
         <f t="shared" ca="1" si="4"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D14">
         <f t="shared" ca="1" si="5"/>
-        <v>0.677490234375</v>
+        <v>0.117462158203125</v>
       </c>
       <c r="E14">
         <f t="shared" ca="1" si="6"/>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G14">
         <v>13</v>
@@ -5676,21 +5837,21 @@
       <c r="A15" t="s">
         <v>7</v>
       </c>
-      <c r="B15" s="3">
+      <c r="B15" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>11409</v>
+        <v>21774</v>
       </c>
       <c r="C15">
         <f t="shared" ca="1" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D15">
         <f t="shared" ca="1" si="5"/>
-        <v>0.348175048828125</v>
+        <v>0.66448974609375</v>
       </c>
       <c r="E15">
         <f t="shared" ca="1" si="6"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G15">
         <v>14</v>
@@ -5748,21 +5909,21 @@
       <c r="A16" t="s">
         <v>8</v>
       </c>
-      <c r="B16" s="3">
+      <c r="B16" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>22518</v>
+        <v>11055</v>
       </c>
       <c r="C16">
         <f t="shared" ca="1" si="4"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D16">
         <f t="shared" ca="1" si="5"/>
-        <v>0.68719482421875</v>
+        <v>0.337371826171875</v>
       </c>
       <c r="E16">
         <f t="shared" ca="1" si="6"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G16">
         <v>15</v>
@@ -5820,21 +5981,21 @@
       <c r="A17" t="s">
         <v>9</v>
       </c>
-      <c r="B17" s="3">
+      <c r="B17" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>6135</v>
+        <v>25916</v>
       </c>
       <c r="C17">
         <f t="shared" ca="1" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D17">
         <f t="shared" ca="1" si="5"/>
-        <v>0.187225341796875</v>
+        <v>0.7908935546875</v>
       </c>
       <c r="E17">
         <f t="shared" ca="1" si="6"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G17">
         <v>16</v>
@@ -5892,9 +6053,9 @@
       <c r="A18" t="s">
         <v>10</v>
       </c>
-      <c r="B18" s="3">
+      <c r="B18" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>9828</v>
+        <v>4805</v>
       </c>
       <c r="C18">
         <f t="shared" ca="1" si="4"/>
@@ -5902,20 +6063,20 @@
       </c>
       <c r="D18">
         <f t="shared" ca="1" si="5"/>
-        <v>0.2999267578125</v>
+        <v>0.146636962890625</v>
       </c>
       <c r="E18">
         <f t="shared" ca="1" si="6"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:23">
       <c r="A19" t="s">
         <v>11</v>
       </c>
-      <c r="B19" s="3">
+      <c r="B19" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>205</v>
+        <v>13338</v>
       </c>
       <c r="C19">
         <f t="shared" ca="1" si="4"/>
@@ -5923,20 +6084,20 @@
       </c>
       <c r="D19">
         <f t="shared" ca="1" si="5"/>
-        <v>6.256103515625E-3</v>
+        <v>0.40704345703125</v>
       </c>
       <c r="E19">
         <f t="shared" ca="1" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:23">
       <c r="A20" t="s">
         <v>12</v>
       </c>
-      <c r="B20" s="3">
+      <c r="B20" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>32130</v>
+        <v>19275</v>
       </c>
       <c r="C20">
         <f t="shared" ca="1" si="4"/>
@@ -5944,20 +6105,20 @@
       </c>
       <c r="D20">
         <f t="shared" ca="1" si="5"/>
-        <v>0.98052978515625</v>
+        <v>0.588226318359375</v>
       </c>
       <c r="E20">
         <f t="shared" ca="1" si="6"/>
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21" spans="1:23">
       <c r="A21" t="s">
         <v>13</v>
       </c>
-      <c r="B21" s="3">
+      <c r="B21" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>15507</v>
+        <v>6440</v>
       </c>
       <c r="C21">
         <f t="shared" ca="1" si="4"/>
@@ -5965,42 +6126,42 @@
       </c>
       <c r="D21">
         <f t="shared" ca="1" si="5"/>
-        <v>0.473236083984375</v>
+        <v>0.196533203125</v>
       </c>
       <c r="E21">
         <f t="shared" ca="1" si="6"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:23">
       <c r="A22" t="s">
         <v>14</v>
       </c>
-      <c r="B22" s="3">
+      <c r="B22" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>17616</v>
+        <v>5697</v>
       </c>
       <c r="C22">
         <f t="shared" ca="1" si="4"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D22">
         <f t="shared" ca="1" si="5"/>
-        <v>0.53759765625</v>
+        <v>0.173858642578125</v>
       </c>
       <c r="E22">
         <f t="shared" ca="1" si="6"/>
-        <v>3</v>
-      </c>
-      <c r="M22" s="3"/>
+        <v>0</v>
+      </c>
+      <c r="M22" s="2"/>
     </row>
     <row r="23" spans="1:23">
       <c r="A23" t="s">
         <v>15</v>
       </c>
-      <c r="B23" s="3">
+      <c r="B23" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>23753</v>
+        <v>30694</v>
       </c>
       <c r="C23">
         <f t="shared" ca="1" si="4"/>
@@ -6008,21 +6169,21 @@
       </c>
       <c r="D23">
         <f t="shared" ca="1" si="5"/>
-        <v>0.724884033203125</v>
+        <v>0.93670654296875</v>
       </c>
       <c r="E23">
         <f t="shared" ca="1" si="6"/>
-        <v>3</v>
-      </c>
-      <c r="M23" s="3"/>
+        <v>4</v>
+      </c>
+      <c r="M23" s="2"/>
     </row>
     <row r="24" spans="1:23">
       <c r="A24" t="s">
         <v>16</v>
       </c>
-      <c r="B24" s="3">
+      <c r="B24" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>28622</v>
+        <v>20775</v>
       </c>
       <c r="C24">
         <f t="shared" ca="1" si="4"/>
@@ -6030,21 +6191,21 @@
       </c>
       <c r="D24">
         <f t="shared" ca="1" si="5"/>
-        <v>0.87347412109375</v>
+        <v>0.634002685546875</v>
       </c>
       <c r="E24">
         <f t="shared" ca="1" si="6"/>
-        <v>4</v>
-      </c>
-      <c r="M24" s="3"/>
+        <v>3</v>
+      </c>
+      <c r="M24" s="2"/>
     </row>
     <row r="25" spans="1:23">
       <c r="A25" t="s">
         <v>17</v>
       </c>
-      <c r="B25" s="3">
+      <c r="B25" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>3823</v>
+        <v>8148</v>
       </c>
       <c r="C25">
         <f t="shared" ca="1" si="4"/>
@@ -6052,21 +6213,21 @@
       </c>
       <c r="D25">
         <f t="shared" ca="1" si="5"/>
-        <v>0.116668701171875</v>
+        <v>0.2486572265625</v>
       </c>
       <c r="E25">
         <f t="shared" ca="1" si="6"/>
         <v>0</v>
       </c>
-      <c r="M25" s="3"/>
+      <c r="M25" s="2"/>
     </row>
     <row r="26" spans="1:23">
       <c r="A26" t="s">
         <v>18</v>
       </c>
-      <c r="B26" s="3">
+      <c r="B26" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>24060</v>
+        <v>21885</v>
       </c>
       <c r="C26">
         <f t="shared" ca="1" si="4"/>
@@ -6074,87 +6235,87 @@
       </c>
       <c r="D26">
         <f t="shared" ca="1" si="5"/>
-        <v>0.7342529296875</v>
+        <v>0.667877197265625</v>
       </c>
       <c r="E26">
         <f t="shared" ca="1" si="6"/>
         <v>3</v>
       </c>
-      <c r="M26" s="3"/>
+      <c r="M26" s="2"/>
     </row>
     <row r="27" spans="1:23">
       <c r="A27" t="s">
         <v>19</v>
       </c>
-      <c r="B27" s="3">
+      <c r="B27" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>31877</v>
+        <v>11378</v>
       </c>
       <c r="C27">
         <f t="shared" ca="1" si="4"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D27">
         <f t="shared" ca="1" si="5"/>
-        <v>0.972808837890625</v>
+        <v>0.34722900390625</v>
       </c>
       <c r="E27">
         <f t="shared" ca="1" si="6"/>
-        <v>4</v>
-      </c>
-      <c r="M27" s="3"/>
+        <v>1</v>
+      </c>
+      <c r="M27" s="2"/>
     </row>
     <row r="28" spans="1:23">
       <c r="A28" t="s">
         <v>20</v>
       </c>
-      <c r="B28" s="3">
+      <c r="B28" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>15066</v>
+        <v>22723</v>
       </c>
       <c r="C28">
         <f t="shared" ca="1" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D28">
         <f t="shared" ca="1" si="5"/>
-        <v>0.45977783203125</v>
+        <v>0.693450927734375</v>
       </c>
       <c r="E28">
         <f t="shared" ca="1" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="M28" s="3"/>
+        <v>3</v>
+      </c>
+      <c r="M28" s="2"/>
     </row>
     <row r="29" spans="1:23">
       <c r="A29" t="s">
         <v>21</v>
       </c>
-      <c r="B29" s="3">
+      <c r="B29" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>11019</v>
+        <v>25920</v>
       </c>
       <c r="C29">
         <f t="shared" ca="1" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D29">
         <f t="shared" ca="1" si="5"/>
-        <v>0.336273193359375</v>
+        <v>0.791015625</v>
       </c>
       <c r="E29">
         <f t="shared" ca="1" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="M29" s="3"/>
+        <v>4</v>
+      </c>
+      <c r="M29" s="2"/>
     </row>
     <row r="30" spans="1:23">
       <c r="A30" t="s">
         <v>22</v>
       </c>
-      <c r="B30" s="3">
+      <c r="B30" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>24040</v>
+        <v>19577</v>
       </c>
       <c r="C30">
         <f t="shared" ca="1" si="4"/>
@@ -6162,43 +6323,43 @@
       </c>
       <c r="D30">
         <f t="shared" ca="1" si="5"/>
-        <v>0.733642578125</v>
+        <v>0.597442626953125</v>
       </c>
       <c r="E30">
         <f t="shared" ca="1" si="6"/>
         <v>3</v>
       </c>
-      <c r="M30" s="3"/>
+      <c r="M30" s="2"/>
     </row>
     <row r="31" spans="1:23">
       <c r="A31" t="s">
         <v>23</v>
       </c>
-      <c r="B31" s="3">
+      <c r="B31" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>23553</v>
+        <v>7614</v>
       </c>
       <c r="C31">
         <f t="shared" ca="1" si="4"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D31">
         <f t="shared" ca="1" si="5"/>
-        <v>0.718780517578125</v>
+        <v>0.23236083984375</v>
       </c>
       <c r="E31">
         <f t="shared" ca="1" si="6"/>
-        <v>3</v>
-      </c>
-      <c r="M31" s="3"/>
+        <v>0</v>
+      </c>
+      <c r="M31" s="2"/>
     </row>
     <row r="32" spans="1:23">
       <c r="A32" t="s">
         <v>24</v>
       </c>
-      <c r="B32" s="3">
+      <c r="B32" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>10918</v>
+        <v>15903</v>
       </c>
       <c r="C32">
         <f t="shared" ca="1" si="4"/>
@@ -6206,71 +6367,71 @@
       </c>
       <c r="D32">
         <f t="shared" ca="1" si="5"/>
-        <v>0.33319091796875</v>
+        <v>0.485321044921875</v>
       </c>
       <c r="E32">
         <f t="shared" ca="1" si="6"/>
         <v>1</v>
       </c>
-      <c r="M32" s="3"/>
+      <c r="M32" s="2"/>
     </row>
     <row r="33" spans="1:13">
       <c r="A33" t="s">
         <v>25</v>
       </c>
-      <c r="B33" s="3">
+      <c r="B33" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>27879</v>
+        <v>5484</v>
       </c>
       <c r="C33">
         <f t="shared" ca="1" si="4"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D33">
         <f t="shared" ca="1" si="5"/>
-        <v>0.850799560546875</v>
+        <v>0.1673583984375</v>
       </c>
       <c r="E33">
         <f t="shared" ca="1" si="6"/>
-        <v>4</v>
-      </c>
-      <c r="M33" s="3"/>
+        <v>0</v>
+      </c>
+      <c r="M33" s="2"/>
     </row>
     <row r="34" spans="1:13">
-      <c r="M34" s="3"/>
+      <c r="M34" s="2"/>
     </row>
     <row r="35" spans="1:13">
-      <c r="M35" s="3"/>
+      <c r="M35" s="2"/>
     </row>
     <row r="36" spans="1:13">
-      <c r="M36" s="3"/>
+      <c r="M36" s="2"/>
     </row>
     <row r="37" spans="1:13">
-      <c r="M37" s="3"/>
+      <c r="M37" s="2"/>
     </row>
     <row r="38" spans="1:13">
-      <c r="M38" s="3"/>
+      <c r="M38" s="2"/>
     </row>
     <row r="39" spans="1:13">
-      <c r="M39" s="3"/>
+      <c r="M39" s="2"/>
     </row>
     <row r="40" spans="1:13">
-      <c r="M40" s="3"/>
+      <c r="M40" s="2"/>
     </row>
     <row r="41" spans="1:13">
-      <c r="M41" s="3"/>
+      <c r="M41" s="2"/>
     </row>
     <row r="42" spans="1:13">
-      <c r="M42" s="3"/>
+      <c r="M42" s="2"/>
     </row>
     <row r="43" spans="1:13">
-      <c r="M43" s="3"/>
+      <c r="M43" s="2"/>
     </row>
     <row r="44" spans="1:13">
-      <c r="M44" s="3"/>
+      <c r="M44" s="2"/>
     </row>
     <row r="45" spans="1:13">
-      <c r="M45" s="3"/>
+      <c r="M45" s="2"/>
     </row>
   </sheetData>
   <customSheetViews>
@@ -6286,60 +6447,60 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D59B824-3E06-4882-96D4-0DA92A742EAC}">
   <dimension ref="C6:H11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="6" spans="3:8">
-      <c r="C6" s="122" t="s">
-        <v>78</v>
-      </c>
-      <c r="D6" s="122"/>
-      <c r="E6" s="122"/>
-      <c r="F6" s="122"/>
-      <c r="G6" s="122"/>
-      <c r="H6" s="122"/>
+      <c r="C6" s="121" t="s">
+        <v>77</v>
+      </c>
+      <c r="D6" s="121"/>
+      <c r="E6" s="121"/>
+      <c r="F6" s="121"/>
+      <c r="G6" s="121"/>
+      <c r="H6" s="121"/>
     </row>
     <row r="7" spans="3:8">
-      <c r="C7" s="122"/>
-      <c r="D7" s="122"/>
-      <c r="E7" s="122"/>
-      <c r="F7" s="122"/>
-      <c r="G7" s="122"/>
-      <c r="H7" s="122"/>
+      <c r="C7" s="121"/>
+      <c r="D7" s="121"/>
+      <c r="E7" s="121"/>
+      <c r="F7" s="121"/>
+      <c r="G7" s="121"/>
+      <c r="H7" s="121"/>
     </row>
     <row r="8" spans="3:8">
-      <c r="C8" s="122"/>
-      <c r="D8" s="122"/>
-      <c r="E8" s="122"/>
-      <c r="F8" s="122"/>
-      <c r="G8" s="122"/>
-      <c r="H8" s="122"/>
+      <c r="C8" s="121"/>
+      <c r="D8" s="121"/>
+      <c r="E8" s="121"/>
+      <c r="F8" s="121"/>
+      <c r="G8" s="121"/>
+      <c r="H8" s="121"/>
     </row>
     <row r="9" spans="3:8">
-      <c r="C9" s="122"/>
-      <c r="D9" s="122"/>
-      <c r="E9" s="122"/>
-      <c r="F9" s="122"/>
-      <c r="G9" s="122"/>
-      <c r="H9" s="122"/>
+      <c r="C9" s="121"/>
+      <c r="D9" s="121"/>
+      <c r="E9" s="121"/>
+      <c r="F9" s="121"/>
+      <c r="G9" s="121"/>
+      <c r="H9" s="121"/>
     </row>
     <row r="10" spans="3:8">
-      <c r="C10" s="122"/>
-      <c r="D10" s="122"/>
-      <c r="E10" s="122"/>
-      <c r="F10" s="122"/>
-      <c r="G10" s="122"/>
-      <c r="H10" s="122"/>
+      <c r="C10" s="121"/>
+      <c r="D10" s="121"/>
+      <c r="E10" s="121"/>
+      <c r="F10" s="121"/>
+      <c r="G10" s="121"/>
+      <c r="H10" s="121"/>
     </row>
     <row r="11" spans="3:8">
-      <c r="C11" s="122"/>
-      <c r="D11" s="122"/>
-      <c r="E11" s="122"/>
-      <c r="F11" s="122"/>
-      <c r="G11" s="122"/>
-      <c r="H11" s="122"/>
+      <c r="C11" s="121"/>
+      <c r="D11" s="121"/>
+      <c r="E11" s="121"/>
+      <c r="F11" s="121"/>
+      <c r="G11" s="121"/>
+      <c r="H11" s="121"/>
     </row>
   </sheetData>
   <customSheetViews>
